--- a/DesignData/Excel_Masters/WeaponAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/WeaponAssets_Master.xlsx
@@ -9,17 +9,17 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23745" windowHeight="7590"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="10050"/>
   </bookViews>
   <sheets>
-    <sheet name="WeaponAssets_Master" sheetId="1" r:id="rId1"/>
+    <sheet name="WeaponAssets" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="176">
   <si>
     <t>---</t>
   </si>
@@ -42,7 +42,7 @@
     <t>WeaponSkillSetup</t>
   </si>
   <si>
-    <t>ActionFX</t>
+    <t>WeaponFX</t>
   </si>
   <si>
     <t>ItemMesh</t>
@@ -54,43 +54,118 @@
     <t>Icon</t>
   </si>
   <si>
+    <t>Blunt_Cleaner</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>(TagName="Item.Type.Weapon.Melee.Blunt")</t>
+  </si>
+  <si>
+    <t>Melee</t>
+  </si>
+  <si>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaBasicAttack.GA_AreaBasicAttack_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_BasicAttack.GE_Damage_BasicAttack_C'",ProjectileClass=None)</t>
+  </si>
+  <si>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaSkill.GA_AreaSkill_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_BasicAttack.GE_Damage_BasicAttack_C'",ProjectileClass=None)</t>
+  </si>
+  <si>
+    <t>(FXData=None,BasicAttackTag=(TagName=""),SkillTag=(TagName=""),BasicAttackHitTag=(TagName=""),SkillHitTag=(TagName=""))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Cleaner/SKM_Blunt_Cleaner.SKM_Blunt_Cleaner</t>
+  </si>
+  <si>
+    <t>Socket_Weapon_R</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Cleaner.Icon_Blunt_Cleaner</t>
+  </si>
+  <si>
+    <t>Blunt_DefaultBlunt</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Blunt/Blunt_DefaultBlunt/SKM_Blunt_DefaultBlunt.SKM_Blunt_DefaultBlunt</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Default_Blunt.Icon_Default_Blunt</t>
+  </si>
+  <si>
+    <t>Blunt_DevilBat</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Devilbat/SKM_Blunt_Devilbat.SKM_Blunt_Devilbat</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_DevilBat.Icon_Blunt_DevilBat</t>
+  </si>
+  <si>
+    <t>Blunt_Event_01</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Event_01/SKM_Blunt_Event_01.SKM_Blunt_Event_01</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Event_01.Icon_Blunt_Event_01</t>
+  </si>
+  <si>
     <t>Blunt_Merry</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>(TagName="Item.Type.Weapon.Melee.Blunt")</t>
-  </si>
-  <si>
-    <t>Melee</t>
-  </si>
-  <si>
-    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaSkill.GA_AreaSkill_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'",ProjectileClass=None)</t>
-  </si>
-  <si>
-    <t>(ActionFXData=None,BasicAttackTag=(TagName=""),SkillTag=(TagName=""))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Merry/SKM_Blunt_Merry.SKM_Blunt_Merry</t>
-  </si>
-  <si>
-    <t>Socket_Weapon_R</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Merry.DA_WeaponFX_Blunt_Merry",BasicAttackTag=(TagName="FX.Weapon.Blunt.Merry.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Merry.Skill"),BasicAttackHitTag=(TagName="FX.Weapon"),SkillHitTag=(TagName=""))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Blunt/Merry/SKM_Blunt_Merry.SKM_Blunt_Merry</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Merry.Icon_Blunt_Merry</t>
   </si>
   <si>
-    <t>Blunt_DefaultBlunt</t>
-  </si>
-  <si>
-    <t>(ActionFXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt.DA_WeaponFX_Blunt",BasicAttackTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.Skill"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_DefaultBlunt/SKM_Blunt_DefaultBlunt.SKM_Blunt_DefaultBlunt</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_DefaultBlunt/T_Blunt_DefaultBlunt.T_Blunt_DefaultBlunt</t>
+    <t>Blunt_Noble</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Blunt/Noble/SKM_Blunt_Nobel_Scaled.SKM_Blunt_Nobel_Scaled</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Nobel.Icon_Blunt_Nobel</t>
+  </si>
+  <si>
+    <t>Blunt_Nurse</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Nurse/SKM_Blunt_Nurse.SKM_Blunt_Nurse</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Nurse.Icon_Blunt_Nurse</t>
+  </si>
+  <si>
+    <t>Blunt_Outsider</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Outsider/SKM_Blunt_Outsider.SKM_Blunt_Outsider</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Outsider.Icon_Blunt_Outsider</t>
+  </si>
+  <si>
+    <t>Blunt_TreasureChest</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Blunt/Blunt_TreasureChest/SKM_Blunt_TreasureChest.SKM_Blunt_TreasureChest</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_TreasureChest.Icon_Blunt_TreasureChest</t>
+  </si>
+  <si>
+    <t>Blunt_Tuner</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Tuner/SKM_Blunt_Tuner.SKM_Blunt_Tuner</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Tuner.Icon_Blunt_Tuner</t>
   </si>
   <si>
     <t>Blunt_Wrench</t>
@@ -102,106 +177,52 @@
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Wrench.Icon_Blunt_Wrench</t>
   </si>
   <si>
-    <t>Blunt_Cleaner</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Cleaner/SKM_Blunt_Cleaner.SKM_Blunt_Cleaner</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Cleaner.Icon_Blunt_Cleaner</t>
-  </si>
-  <si>
-    <t>Blunt_Noble</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Noble/SKM_Blunt_Noble.SKM_Blunt_Noble</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Noble/T_Blunt_Noble0.T_Blunt_Noble0</t>
-  </si>
-  <si>
-    <t>Blunt_Nurse</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Nurse/SKM_Blunt_Nurse.SKM_Blunt_Nurse</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Nurse/T_Blunt_Nurse.T_Blunt_Nurse</t>
-  </si>
-  <si>
-    <t>Blunt_Tuner</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Tuner/SKM_Blunt_Tuner.SKM_Blunt_Tuner</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Tuner/T_Blunt_Tuner.T_Blunt_Tuner</t>
-  </si>
-  <si>
-    <t>Blunt_DevilBat</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Devilbat/SKM_Blunt_Devilbat.SKM_Blunt_Devilbat</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_DevilBat.Icon_Blunt_DevilBat</t>
-  </si>
-  <si>
-    <t>Blunt_Outsider</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Outsider/SKM_Blunt_Outsider.SKM_Blunt_Outsider</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Outsider/T_Blunt_Outsider.T_Blunt_Outsider</t>
-  </si>
-  <si>
-    <t>Blunt_Event_01</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Event_01/SKM_Blunt_Event_01.SKM_Blunt_Event_01</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Event_01.Icon_Blunt_Event_01</t>
-  </si>
-  <si>
-    <t>Blunt_TreasureChest</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_TreasureChest/SKM_Blunt_TreasureChest.SKM_Blunt_TreasureChest</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_TreasureChest.Icon_Blunt_TreasureChest</t>
+    <t>Book_BookOfRed</t>
+  </si>
+  <si>
+    <t>(TagName="Item.Type.Weapon.Range.Book")</t>
+  </si>
+  <si>
+    <t>Book</t>
+  </si>
+  <si>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileBasicAttack.GA_ProjectileBasicAttack_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_BasicAttack.GE_Damage_BasicAttack_C'",ProjectileClass=None)</t>
+  </si>
+  <si>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileSkill.GA_ProjectileSkill_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_BasicAttack.GE_Damage_BasicAttack_C'",ProjectileClass=None)</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Book/Book_BookOfRedMage/SKM_Book_BookOfRedMage1.SKM_Book_BookOfRedMage1</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_12021_BookOfRedMage.Icon_Book_12021_BookOfRedMage</t>
+  </si>
+  <si>
+    <t>Book_CookingForDummies</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Book/Book_CookingForDummies/SKM_Book_CookingForDummies.SKM_Book_CookingForDummies</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_12041_CookingForDummies.Icon_Book_12041_CookingForDummies</t>
+  </si>
+  <si>
+    <t>Book_DeckCase</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Book/DeckCase/SKM_Book_DeckCase1.SKM_Book_DeckCase1</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_12061_DeckCase.Icon_Book_12061_DeckCase</t>
   </si>
   <si>
     <t>Book_DefaultBook</t>
   </si>
   <si>
-    <t>(TagName="Item.Type.Weapon.Range.Book")</t>
-  </si>
-  <si>
-    <t>Book</t>
-  </si>
-  <si>
-    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileBasicAttack.GA_ProjectileBasicAttack_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'",ProjectileClass="/Script/CoreUObject.Class'/Script/Paradise.ProjectileSingleTarget'")</t>
-  </si>
-  <si>
-    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileSkill.GA_ProjectileSkill_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'",ProjectileClass="/Script/CoreUObject.Class'/Script/Paradise.ProjectilePiercing'")</t>
-  </si>
-  <si>
     <t>/Game/External_Assets/Weapon/Book/Book_DefaultBook/SKM_Book_DefaultBook.SKM_Book_DefaultBook</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_DefaultBook/T_Book_DefaultBook.T_Book_DefaultBook</t>
-  </si>
-  <si>
-    <t>Book_CookingForDummies</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_CookingForDummies/SKM_Book_CookingForDummies.SKM_Book_CookingForDummies</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_12041_CookingForDummies.Icon_Book_12041_CookingForDummies</t>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_DefaultBook.Icon_Book_DefaultBook</t>
   </si>
   <si>
     <t>Book_Dictionary</t>
@@ -213,13 +234,22 @@
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_12011_Dictionary.Icon_Book_12011_Dictionary</t>
   </si>
   <si>
-    <t>Book_DeckCase</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_DeckCase/SKM_Book_DeckCase1.SKM_Book_DeckCase1</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_12061_DeckCase.Icon_Book_12061_DeckCase</t>
+    <t>Book_Event_01</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Book/Book_Event_01/SKM_Book_Event_01.SKM_Book_Event_01</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_Event_01.Icon_Book_Event_01</t>
+  </si>
+  <si>
+    <t>Book_FlawlessPlaying</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Book/Book_FlawlessPlaying/SKM_Book_FlawlessPlaying1.SKM_Book_FlawlessPlaying1</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_FlawlessPlaying.Icon_Book_FlawlessPlaying</t>
   </si>
   <si>
     <t>Book_HologramHud</t>
@@ -228,7 +258,16 @@
     <t>/Game/External_Assets/Weapon/Book/Book_HologramHud/SKM_Book_HologramHud1.SKM_Book_HologramHud1</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_HologramHud/T_Book_HologramHud.T_Book_HologramHud</t>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_Courier.Icon_Book_Courier</t>
+  </si>
+  <si>
+    <t>Book_MementoMori</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Book/Book_Mementomori/SKM_Book_MementoMori1.SKM_Book_MementoMori1</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_Hermit.Icon_Book_Hermit</t>
   </si>
   <si>
     <t>Book_PerfectHarmony</t>
@@ -237,198 +276,204 @@
     <t>/Game/External_Assets/Weapon/Book/Book_PerfectHarmony/SKM_Book_PerfectHarmony.SKM_Book_PerfectHarmony</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_PerfectHarmony/T_Book_PerfectHarmony.T_Book_PerfectHarmony</t>
-  </si>
-  <si>
-    <t>Book_BookOfRed</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_BookOfRedMage/SKM_Book_BookOfRedMage1.SKM_Book_BookOfRedMage1</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_12021_BookOfRedMage.Icon_Book_12021_BookOfRedMage</t>
-  </si>
-  <si>
-    <t>Book_MementoMori</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_Mementomori/SKM_Book_MementoMori1.SKM_Book_MementoMori1</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_Mementomori/T_Book_MementoMori.T_Book_MementoMori</t>
-  </si>
-  <si>
-    <t>Book_Event_01</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_Event_01/SKM_Book_Event_01.SKM_Book_Event_01</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_Event_01.Icon_Book_Event_01</t>
-  </si>
-  <si>
-    <t>Book_FlawlessPlaying</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_FlawlessPlaying/SKM_Book_FlawlessPlaying1.SKM_Book_FlawlessPlaying1</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_FlawlessPlaying/T_Book_FlawlessPlaying.T_Book_FlawlessPlaying</t>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_PerfectHarmony.Icon_Book_PerfectHarmony</t>
+  </si>
+  <si>
+    <t>Gun_BlackBeard</t>
+  </si>
+  <si>
+    <t>(TagName="Item.Type.Weapon.Range.Gun")</t>
+  </si>
+  <si>
+    <t>Gun</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Gun/BlackBeard/SKM_Gun_Blackbeard_Scaled.SKM_Gun_Blackbeard_Scaled</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13041_BlackBeard.Icon_Gun_13041_BlackBeard</t>
   </si>
   <si>
     <t>Gun_BlackNose</t>
   </si>
   <si>
-    <t>(TagName="Item.Type.Weapon.Range.Gun")</t>
-  </si>
-  <si>
-    <t>Gun</t>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileBasicAttack.GA_ProjectileBasicAttack_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_BasicAttack.GE_Damage_BasicAttack_C'",ProjectileClass="/Script/Engine.BlueprintGeneratedClass'/Game/Blueprints/Object/Projectile/BP_Bullet.BP_Bullet_C'")</t>
+  </si>
+  <si>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileSkill.GA_ProjectileSkill_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Skill.GE_Damage_Skill_C'",ProjectileClass="/Script/Engine.BlueprintGeneratedClass'/Game/Blueprints/Object/Projectile/BP_Bullet.BP_Bullet_C'")</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_BlackNose.DA_WeaponFX_Gun_BlackNose",BasicAttackTag=(TagName="FX.Weapon.Gun.BlackNose.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.BlackNose.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.BlackNose.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.BlackNose.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Gun/Gun_BlackNose/SKM_Gun_BlackNose.SKM_Gun_BlackNose</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Weapon/Gun/Gun_BlackNose/T_Gun_BlackNose.T_Gun_BlackNose</t>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_BlackNose.Icon_Gun_BlackNose</t>
+  </si>
+  <si>
+    <t>Gun_Demonia</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Demonia/SKM_Gun_Demonia.SKM_Gun_Demonia</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_Demonia.Icon_Gun_Demonia</t>
+  </si>
+  <si>
+    <t>Gun_Event_01</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Event_01/SKM_Gun_Event_01.SKM_Gun_Event_01</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_Event_01.Icon_Gun_Event_01</t>
+  </si>
+  <si>
+    <t>Gun_LovelyCoil</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Lovelycoil/SKM_Gun_Lovelycoil_Scaled.SKM_Gun_Lovelycoil_Scaled</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13051_LovelyCoil.Icon_Gun_13051_LovelyCoil</t>
+  </si>
+  <si>
+    <t>Gun_Mustang</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Mustang/SKM_Gun_Mustang_Scaled.SKM_Gun_Mustang_Scaled</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13061_Mustang.Icon_Gun_13061_Mustang</t>
+  </si>
+  <si>
+    <t>Gun_Nail_Gun</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Gun/DefaultGun/SKM_Gun_DefaultGun.SKM_Gun_DefaultGun</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_NailGun.Icon_Gun_NailGun</t>
+  </si>
+  <si>
+    <t>Gun_PayBack</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Payback/SKM_Gun_Payback_Scaled.SKM_Gun_Payback_Scaled</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13011_PayBack.Icon_Gun_13011_PayBack</t>
   </si>
   <si>
     <t>Gun_Smithers</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Weapon/Gun/Gun_DefaultGun/SKM_Gun_Smithers.SKM_Gun_Smithers</t>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Smithers/SKM_Gun_Smithers_Scaled.SKM_Gun_Smithers_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_Smithers.Icon_Gun_Smithers</t>
   </si>
   <si>
-    <t>Gun_Nail_Gun</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Gun/Gun_DefaultGun/SKM_Gun_Nailgun.SKM_Gun_Nailgun</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_NailGun.Icon_Gun_NailGun</t>
-  </si>
-  <si>
-    <t>Gun_LovelyCoil</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Gun/Gun_DefaultGun/SKM_Gun_Lovelycoil.SKM_Gun_Lovelycoil</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13051_LovelyCoil.Icon_Gun_13051_LovelyCoil</t>
-  </si>
-  <si>
-    <t>Gun_Mustang</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Gun/Gun_DefaultGun/SKM_Gun_Mustang.SKM_Gun_Mustang</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13061_Mustang.Icon_Gun_13061_Mustang</t>
-  </si>
-  <si>
-    <t>Gun_PayBack</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Gun/Gun_DefaultGun/SKM_Gun_Payback.SKM_Gun_Payback</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13011_PayBack.Icon_Gun_13011_PayBack</t>
-  </si>
-  <si>
-    <t>Gun_Demonia</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Gun/Gun_DefaultGun/SKM_Gun_Demonia.SKM_Gun_Demonia</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_Demonia.Icon_Gun_Demonia</t>
-  </si>
-  <si>
-    <t>Gun_Event_01</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Gun/Gun_DefaultGun/SKM_Gun_Event_01.SKM_Gun_Event_01</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_Event_01.Icon_Gun_Event_01</t>
-  </si>
-  <si>
-    <t>Gun_BlackBeard</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Gun/Gun_Blackbeard/SKM_Gun_Blackbeard1.SKM_Gun_Blackbeard1</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13041_BlackBeard.Icon_Gun_13041_BlackBeard</t>
+    <t>Staff_Anubis</t>
+  </si>
+  <si>
+    <t>(TagName="Item.Type.Weapon.Range.Staff")</t>
+  </si>
+  <si>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileSkill.GA_ProjectileSkill_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_BasicAttack.GE_Damage_BasicAttack_C'",ProjectileClass="/Script/Engine.BlueprintGeneratedClass'/Game/Blueprints/Object/Projectile/BP_Bullet.BP_Bullet_C'")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Staff/Staff_Anubis/SKM_Staff_Anubis.SKM_Staff_Anubis</t>
+  </si>
+  <si>
+    <t>Staff_Binder</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Staff/Staff_Binder/SKM_Staff_Binder.SKM_Staff_Binder</t>
+  </si>
+  <si>
+    <t>Staff_DeathMatch</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Staff/Staff_Deathmatch/SKM_Staff_Deathmatch.SKM_Staff_Deathmatch</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11031_DeathMatch.Icon_Staff_11031_DeathMatch</t>
+  </si>
+  <si>
+    <t>Staff_Decanter</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Staff/Staff_Decanter/SKM_Staff_Decanter.SKM_Staff_Decanter</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11051_Decanter.Icon_Staff_11051_Decanter</t>
+  </si>
+  <si>
+    <t>Staff_DefaultStaff</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Staff/Staff_DefaultStaff/SKM_Staff_DefaultStaff.SKM_Staff_DefaultStaff</t>
+  </si>
+  <si>
+    <t>Staff_Event_01</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Staff/Staff_Event_01/SKM_Staff_Event_01.SKM_Staff_Event_01</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_Event_01.Icon_Staff_Event_01</t>
   </si>
   <si>
     <t>Staff_GazeOfDragon</t>
   </si>
   <si>
-    <t>(TagName="Item.Type.Weapon.Range.Staff")</t>
-  </si>
-  <si>
     <t>/Game/External_Assets/Weapon/Staff/Staff_GazeOfDragon/SKM_Staff_GazeOfDragon.SKM_Staff_GazeOfDragon</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_Rogue.Icon_Staff_Rogue</t>
   </si>
   <si>
+    <t>Staff_Initiator</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Staff/Staff_Initiator/SKM_Staff_Initiator.SKM_Staff_Initiator</t>
+  </si>
+  <si>
+    <t>Staff_OneStroke</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Staff/Staff_OneStroke/SKM_Staff_OneStroke.SKM_Staff_OneStroke</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11041_OneStroke.Icon_Staff_11041_OneStroke</t>
+  </si>
+  <si>
+    <t>Staff_OverTheHorizon</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Staff/Staff_OverTheHorizon/SKM_Staff_OverTheHorizon.SKM_Staff_OverTheHorizon</t>
+  </si>
+  <si>
     <t>Staff_StandUp</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Weapon/Staff/Staff_Anubis/SKM_Staff_StandUp.SKM_Staff_StandUp</t>
+    <t>/Game/External_Assets/Weapon/Staff/Staff_StandUp/SKM_Staff_StandUp.SKM_Staff_StandUp</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_Bard.Icon_Staff_Bard</t>
   </si>
   <si>
-    <t>Staff_OneStroke</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Staff/Staff_Anubis/SKM_Staff_OneStroke.SKM_Staff_OneStroke</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11041_OneStroke.Icon_Staff_11041_OneStroke</t>
-  </si>
-  <si>
-    <t>Staff_Decanter</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Staff/Staff_Anubis/SKM_Staff_Decanter.SKM_Staff_Decanter</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11051_Decanter.Icon_Staff_11051_Decanter</t>
-  </si>
-  <si>
-    <t>Staff_DeathMatch</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Staff/Staff_Deathmatch/SKM_Staff_Deathmatch.SKM_Staff_Deathmatch</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11031_DeathMatch.Icon_Staff_11031_DeathMatch</t>
-  </si>
-  <si>
     <t>Staff_WinterCane</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Weapon/Staff/Staff_Anubis/SKM_Staff_Wintercane.SKM_Staff_Wintercane</t>
+    <t>/Game/External_Assets/Weapon/Staff/Staff_Wintercane/SKM_Staff_Wintercane.SKM_Staff_Wintercane</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11061_WinterCane.Icon_Staff_11061_WinterCane</t>
   </si>
   <si>
-    <t>Staff_Event_01</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Staff/Staff_Anubis/SKM_Staff_Event_01.SKM_Staff_Event_01</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_Event_01.Icon_Staff_Event_01</t>
-  </si>
-  <si>
     <t>Sword_Army</t>
   </si>
   <si>
@@ -441,6 +486,15 @@
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_Army.Icon_Sword_Army</t>
   </si>
   <si>
+    <t>Sword_BeamSword</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_BeamSword.SKM_Sword_BeamSword</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_BeamSword.Icon_Sword_BeamSword</t>
+  </si>
+  <si>
     <t>Sword_ButterSlayer</t>
   </si>
   <si>
@@ -450,13 +504,31 @@
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_ButterSlayer.Icon_Sword_ButterSlayer</t>
   </si>
   <si>
+    <t>Sword_ChainSword</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_ChainSword.SKM_Sword_ChainSword</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_ChainSword.Icon_Sword_ChainSword</t>
+  </si>
+  <si>
+    <t>Sword_Event_01</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_Event_01.SKM_Sword_Event_01</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_Event_01.Icon_Sword_Event_01</t>
+  </si>
+  <si>
     <t>Sword_HonetBlade</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_MilkyWay.SKM_Sword_MilkyWay</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Weapon/Sword/Sword_HornetBlade/T_Sword_HornetBlade.T_Sword_HornetBlade</t>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_HonetBlade.Icon_Sword_HonetBlade</t>
   </si>
   <si>
     <t>Sword_Maid</t>
@@ -468,41 +540,13 @@
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_Maid.Icon_Sword_Maid</t>
   </si>
   <si>
-    <t>Sword_BeamSword</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_BeamSword.SKM_Sword_BeamSword</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_BeamSword.Icon_Sword_BeamSword</t>
-  </si>
-  <si>
-    <t>Sword_ChainSword</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_ChainSword.SKM_Sword_ChainSword</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_ChainSword.Icon_Sword_ChainSword</t>
-  </si>
-  <si>
-    <t>Sword_Event_01</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_Event_01.SKM_Sword_Event_01</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_Event_01.Icon_Sword_Event_01</t>
-  </si>
-  <si>
     <t>Sword_MilkyWay</t>
   </si>
   <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Sword/Carver/SKM_Sword_Carver_Scaled.SKM_Sword_Carver_Scaled</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_MilkWay.Icon_Sword_MilkWay</t>
-  </si>
-  <si>
-    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaBasicAttack.GA_AreaBasicAttack_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'",ProjectileClass=None)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1420,7 +1464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -1475,27 +1519,27 @@
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -1510,19 +1554,19 @@
         <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
       </c>
       <c r="J3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K3" t="s">
         <v>23</v>
@@ -1545,19 +1589,19 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
         <v>25</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K4" t="s">
         <v>26</v>
@@ -1580,19 +1624,19 @@
         <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
         <v>28</v>
       </c>
       <c r="J5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K5" t="s">
         <v>29</v>
@@ -1615,27 +1659,27 @@
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="I6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -1650,27 +1694,27 @@
         <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -1685,27 +1729,27 @@
         <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -1720,27 +1764,27 @@
         <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -1755,27 +1799,27 @@
         <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -1790,27 +1834,27 @@
         <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -1825,27 +1869,27 @@
         <v>14</v>
       </c>
       <c r="F12" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -1854,33 +1898,33 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -1889,33 +1933,33 @@
         <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
@@ -1924,33 +1968,33 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
@@ -1959,33 +2003,33 @@
         <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
@@ -1994,33 +2038,33 @@
         <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
@@ -2029,33 +2073,33 @@
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
@@ -2064,33 +2108,33 @@
         <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
@@ -2099,33 +2143,33 @@
         <v>12</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
@@ -2134,33 +2178,33 @@
         <v>12</v>
       </c>
       <c r="D21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B22" t="s">
         <v>12</v>
@@ -2169,33 +2213,33 @@
         <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
@@ -2204,33 +2248,33 @@
         <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
@@ -2239,33 +2283,33 @@
         <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F24" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="G24" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="I24" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K24" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
@@ -2274,33 +2318,33 @@
         <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K25" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
@@ -2309,33 +2353,33 @@
         <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I26" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="J26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K26" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B27" t="s">
         <v>12</v>
@@ -2344,33 +2388,33 @@
         <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I27" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K27" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B28" t="s">
         <v>12</v>
@@ -2379,33 +2423,33 @@
         <v>12</v>
       </c>
       <c r="D28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I28" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="J28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K28" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B29" t="s">
         <v>12</v>
@@ -2414,33 +2458,33 @@
         <v>12</v>
       </c>
       <c r="D29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I29" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="J29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K29" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
@@ -2449,33 +2493,33 @@
         <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I30" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="J30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K30" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B31" t="s">
         <v>12</v>
@@ -2484,33 +2528,33 @@
         <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I31" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="J31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K31" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B32" t="s">
         <v>12</v>
@@ -2519,33 +2563,33 @@
         <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F32" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="G32" t="s">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="H32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I32" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K32" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B33" t="s">
         <v>12</v>
@@ -2554,33 +2598,33 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F33" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G33" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I33" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="J33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K33" t="s">
-        <v>120</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
@@ -2589,33 +2633,33 @@
         <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F34" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I34" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K34" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B35" t="s">
         <v>12</v>
@@ -2624,33 +2668,33 @@
         <v>12</v>
       </c>
       <c r="D35" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E35" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I35" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K35" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
@@ -2659,33 +2703,33 @@
         <v>12</v>
       </c>
       <c r="D36" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F36" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I36" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K36" t="s">
-        <v>129</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B37" t="s">
         <v>12</v>
@@ -2694,33 +2738,33 @@
         <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E37" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="F37" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G37" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H37" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I37" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B38" t="s">
         <v>12</v>
@@ -2729,33 +2773,33 @@
         <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E38" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="F38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K38" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B39" t="s">
         <v>12</v>
@@ -2764,28 +2808,28 @@
         <v>12</v>
       </c>
       <c r="D39" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="E39" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="F39" t="s">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="G39" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="H39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K39" t="s">
-        <v>139</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
@@ -2799,25 +2843,25 @@
         <v>12</v>
       </c>
       <c r="D40" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="E40" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="F40" t="s">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="G40" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="H40" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I40" t="s">
         <v>141</v>
       </c>
       <c r="J40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K40" t="s">
         <v>142</v>
@@ -2834,130 +2878,130 @@
         <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="E41" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="F41" t="s">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="G41" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="H41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I41" t="s">
         <v>144</v>
       </c>
       <c r="J41" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K41" t="s">
-        <v>145</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>145</v>
+      </c>
+      <c r="B42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s">
+        <v>119</v>
+      </c>
+      <c r="E42" t="s">
+        <v>54</v>
+      </c>
+      <c r="F42" t="s">
+        <v>55</v>
+      </c>
+      <c r="G42" t="s">
+        <v>56</v>
+      </c>
+      <c r="H42" t="s">
+        <v>17</v>
+      </c>
+      <c r="I42" t="s">
         <v>146</v>
       </c>
-      <c r="B42" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" t="s">
-        <v>12</v>
-      </c>
-      <c r="D42" t="s">
-        <v>137</v>
-      </c>
-      <c r="E42" t="s">
-        <v>14</v>
-      </c>
-      <c r="F42" t="s">
-        <v>160</v>
-      </c>
-      <c r="G42" t="s">
-        <v>15</v>
-      </c>
-      <c r="H42" t="s">
-        <v>16</v>
-      </c>
-      <c r="I42" t="s">
+      <c r="J42" t="s">
+        <v>19</v>
+      </c>
+      <c r="K42" t="s">
         <v>147</v>
-      </c>
-      <c r="J42" t="s">
-        <v>18</v>
-      </c>
-      <c r="K42" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>148</v>
+      </c>
+      <c r="B43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" t="s">
+        <v>119</v>
+      </c>
+      <c r="E43" t="s">
+        <v>54</v>
+      </c>
+      <c r="F43" t="s">
+        <v>55</v>
+      </c>
+      <c r="G43" t="s">
+        <v>56</v>
+      </c>
+      <c r="H43" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" t="s">
         <v>149</v>
       </c>
-      <c r="B43" t="s">
-        <v>12</v>
-      </c>
-      <c r="C43" t="s">
-        <v>12</v>
-      </c>
-      <c r="D43" t="s">
-        <v>137</v>
-      </c>
-      <c r="E43" t="s">
-        <v>14</v>
-      </c>
-      <c r="F43" t="s">
-        <v>160</v>
-      </c>
-      <c r="G43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H43" t="s">
-        <v>16</v>
-      </c>
-      <c r="I43" t="s">
+      <c r="J43" t="s">
+        <v>19</v>
+      </c>
+      <c r="K43" t="s">
         <v>150</v>
-      </c>
-      <c r="J43" t="s">
-        <v>18</v>
-      </c>
-      <c r="K43" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>151</v>
+      </c>
+      <c r="B44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" t="s">
         <v>152</v>
-      </c>
-      <c r="B44" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" t="s">
-        <v>12</v>
-      </c>
-      <c r="D44" t="s">
-        <v>137</v>
       </c>
       <c r="E44" t="s">
         <v>14</v>
       </c>
       <c r="F44" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H44" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I44" t="s">
         <v>153</v>
       </c>
       <c r="J44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K44" t="s">
         <v>154</v>
@@ -2974,25 +3018,25 @@
         <v>12</v>
       </c>
       <c r="D45" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="E45" t="s">
         <v>14</v>
       </c>
       <c r="F45" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I45" t="s">
         <v>156</v>
       </c>
       <c r="J45" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K45" t="s">
         <v>157</v>
@@ -3009,28 +3053,203 @@
         <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="E46" t="s">
         <v>14</v>
       </c>
       <c r="F46" t="s">
+        <v>15</v>
+      </c>
+      <c r="G46" t="s">
+        <v>16</v>
+      </c>
+      <c r="H46" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" t="s">
+        <v>159</v>
+      </c>
+      <c r="J46" t="s">
+        <v>19</v>
+      </c>
+      <c r="K46" t="s">
         <v>160</v>
       </c>
-      <c r="G46" t="s">
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>161</v>
+      </c>
+      <c r="B47" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" t="s">
+        <v>152</v>
+      </c>
+      <c r="E47" t="s">
+        <v>14</v>
+      </c>
+      <c r="F47" t="s">
         <v>15</v>
       </c>
-      <c r="H46" t="s">
+      <c r="G47" t="s">
         <v>16</v>
       </c>
-      <c r="I46" t="s">
-        <v>144</v>
-      </c>
-      <c r="J46" t="s">
-        <v>18</v>
-      </c>
-      <c r="K46" t="s">
-        <v>159</v>
+      <c r="H47" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" t="s">
+        <v>162</v>
+      </c>
+      <c r="J47" t="s">
+        <v>19</v>
+      </c>
+      <c r="K47" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>164</v>
+      </c>
+      <c r="B48" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" t="s">
+        <v>152</v>
+      </c>
+      <c r="E48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F48" t="s">
+        <v>15</v>
+      </c>
+      <c r="G48" t="s">
+        <v>16</v>
+      </c>
+      <c r="H48" t="s">
+        <v>17</v>
+      </c>
+      <c r="I48" t="s">
+        <v>165</v>
+      </c>
+      <c r="J48" t="s">
+        <v>19</v>
+      </c>
+      <c r="K48" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>167</v>
+      </c>
+      <c r="B49" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" t="s">
+        <v>152</v>
+      </c>
+      <c r="E49" t="s">
+        <v>14</v>
+      </c>
+      <c r="F49" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" t="s">
+        <v>16</v>
+      </c>
+      <c r="H49" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" t="s">
+        <v>168</v>
+      </c>
+      <c r="J49" t="s">
+        <v>19</v>
+      </c>
+      <c r="K49" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>170</v>
+      </c>
+      <c r="B50" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" t="s">
+        <v>152</v>
+      </c>
+      <c r="E50" t="s">
+        <v>14</v>
+      </c>
+      <c r="F50" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" t="s">
+        <v>16</v>
+      </c>
+      <c r="H50" t="s">
+        <v>17</v>
+      </c>
+      <c r="I50" t="s">
+        <v>171</v>
+      </c>
+      <c r="J50" t="s">
+        <v>19</v>
+      </c>
+      <c r="K50" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>173</v>
+      </c>
+      <c r="B51" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" t="s">
+        <v>152</v>
+      </c>
+      <c r="E51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F51" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" t="s">
+        <v>16</v>
+      </c>
+      <c r="H51" t="s">
+        <v>17</v>
+      </c>
+      <c r="I51" t="s">
+        <v>174</v>
+      </c>
+      <c r="J51" t="s">
+        <v>19</v>
+      </c>
+      <c r="K51" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Excel_Masters/WeaponAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/WeaponAssets_Master.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="10050"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="10035"/>
   </bookViews>
   <sheets>
     <sheet name="WeaponAssets" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="222">
   <si>
     <t>---</t>
   </si>
@@ -69,10 +69,10 @@
     <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaBasicAttack.GA_AreaBasicAttack_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_BasicAttack.GE_Damage_BasicAttack_C'",ProjectileClass=None)</t>
   </si>
   <si>
-    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaSkill.GA_AreaSkill_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_BasicAttack.GE_Damage_BasicAttack_C'",ProjectileClass=None)</t>
-  </si>
-  <si>
-    <t>(FXData=None,BasicAttackTag=(TagName=""),SkillTag=(TagName=""),BasicAttackHitTag=(TagName=""),SkillHitTag=(TagName=""))</t>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaSkill.GA_AreaSkill_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Skill.GE_Damage_Skill_C'",ProjectileClass=None)</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Cleaner.DA_WeaponFX_Blunt_Cleaner",BasicAttackTag=(TagName="FX.Weapon.Blunt.Cleaner.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Cleaner.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Cleaner.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Cleaner.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Blunt/Blunt_Cleaner/SKM_Blunt_Cleaner.SKM_Blunt_Cleaner</t>
@@ -87,6 +87,9 @@
     <t>Blunt_DefaultBlunt</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_DefaultBlunt.DA_WeaponFX_Blunt_DefaultBlunt",BasicAttackTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Blunt/Blunt_DefaultBlunt/SKM_Blunt_DefaultBlunt.SKM_Blunt_DefaultBlunt</t>
   </si>
   <si>
@@ -96,13 +99,19 @@
     <t>Blunt_DevilBat</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Devilbat.DA_WeaponFX_Blunt_Devilbat",BasicAttackTag=(TagName="FX.Weapon.Blunt.DevilBat.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.DevilBat.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.DevilBat.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.DevilBat.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Blunt/Blunt_Devilbat/SKM_Blunt_Devilbat.SKM_Blunt_Devilbat</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_DevilBat.Icon_Blunt_DevilBat</t>
   </si>
   <si>
-    <t>Blunt_Event_01</t>
+    <t>Blunt_EventBlunt</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_EventBlunt.DA_WeaponFX_Blunt_EventBlunt",BasicAttackTag=(TagName="FX.Weapon.Blunt.EventBlunt.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.EventBlunt.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.EventBlunt.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.EventBlunt.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Blunt/Blunt_Event_01/SKM_Blunt_Event_01.SKM_Blunt_Event_01</t>
@@ -114,7 +123,7 @@
     <t>Blunt_Merry</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Merry.DA_WeaponFX_Blunt_Merry",BasicAttackTag=(TagName="FX.Weapon.Blunt.Merry.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Merry.Skill"),BasicAttackHitTag=(TagName="FX.Weapon"),SkillHitTag=(TagName=""))</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Merry.DA_WeaponFX_Blunt_Merry",BasicAttackTag=(TagName="FX.Weapon.Blunt.Merry.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Merry.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Merry.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Merry.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Blunt/Merry/SKM_Blunt_Merry.SKM_Blunt_Merry</t>
@@ -126,6 +135,9 @@
     <t>Blunt_Noble</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Noble.DA_WeaponFX_Blunt_Noble",BasicAttackTag=(TagName="FX.Weapon.Blunt.Noble.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Noble.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Noble.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Noble.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Blunt/Noble/SKM_Blunt_Nobel_Scaled.SKM_Blunt_Nobel_Scaled</t>
   </si>
   <si>
@@ -135,6 +147,9 @@
     <t>Blunt_Nurse</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Nurse.DA_WeaponFX_Blunt_Nurse",BasicAttackTag=(TagName="FX.Weapon.Blunt.Nurse.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Nurse.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Nurse.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Nurse.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Blunt/Blunt_Nurse/SKM_Blunt_Nurse.SKM_Blunt_Nurse</t>
   </si>
   <si>
@@ -144,6 +159,9 @@
     <t>Blunt_Outsider</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Outsider.DA_WeaponFX_Blunt_Outsider",BasicAttackTag=(TagName="FX.Weapon.Blunt.Outsider.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Outsider.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Outsider.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Outsider.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Blunt/Blunt_Outsider/SKM_Blunt_Outsider.SKM_Blunt_Outsider</t>
   </si>
   <si>
@@ -153,6 +171,9 @@
     <t>Blunt_TreasureChest</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_TreasureChest.DA_WeaponFX_Blunt_TreasureChest",BasicAttackTag=(TagName="FX.Weapon.Blunt.TreasureChest.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.TreasureChest.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.TreasureChest.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.TreasureChest.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Blunt/Blunt_TreasureChest/SKM_Blunt_TreasureChest.SKM_Blunt_TreasureChest</t>
   </si>
   <si>
@@ -162,6 +183,9 @@
     <t>Blunt_Tuner</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Tuner.DA_WeaponFX_Blunt_Tuner",BasicAttackTag=(TagName="FX.Weapon.Blunt.Tuner.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Tuner.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Tuner.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Tuner.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Blunt/Blunt_Tuner/SKM_Blunt_Tuner.SKM_Blunt_Tuner</t>
   </si>
   <si>
@@ -171,6 +195,9 @@
     <t>Blunt_Wrench</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Wrench.DA_WeaponFX_Blunt_Wrench",BasicAttackTag=(TagName="FX.Weapon.Blunt.Wrench.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Wrench.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Wrench.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Wrench.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Blunt/Blunt_Wrench/SKM_Blunt_Wrench.SKM_Blunt_Wrench</t>
   </si>
   <si>
@@ -183,13 +210,16 @@
     <t>(TagName="Item.Type.Weapon.Range.Book")</t>
   </si>
   <si>
-    <t>Book</t>
+    <t>Magic</t>
   </si>
   <si>
     <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileBasicAttack.GA_ProjectileBasicAttack_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_BasicAttack.GE_Damage_BasicAttack_C'",ProjectileClass=None)</t>
   </si>
   <si>
-    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileSkill.GA_ProjectileSkill_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_BasicAttack.GE_Damage_BasicAttack_C'",ProjectileClass=None)</t>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileSkill.GA_ProjectileSkill_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Skill.GE_Damage_Skill_C'",ProjectileClass=None)</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_BookOfRed.DA_WeaponFX_Book_BookOfRed",BasicAttackTag=(TagName="FX.Weapon.Book.BookOfRed.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.BookOfRed.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.BookOfRed.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.BookOfRed.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Book/Book_BookOfRedMage/SKM_Book_BookOfRedMage1.SKM_Book_BookOfRedMage1</t>
@@ -201,6 +231,9 @@
     <t>Book_CookingForDummies</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_CookingForDummies.DA_WeaponFX_Book_CookingForDummies",BasicAttackTag=(TagName="FX.Weapon.Book.CookingForDummies.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.CookingForDummies.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.CookingForDummies.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.CookingForDummies.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Book/Book_CookingForDummies/SKM_Book_CookingForDummies.SKM_Book_CookingForDummies</t>
   </si>
   <si>
@@ -210,6 +243,9 @@
     <t>Book_DeckCase</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_EventBook.DA_WeaponFX_Book_EventBook",BasicAttackTag=(TagName="FX.Weapon.Book.DeckCase.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.DeckCase.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.DeckCase.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.DeckCase.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Book/DeckCase/SKM_Book_DeckCase1.SKM_Book_DeckCase1</t>
   </si>
   <si>
@@ -219,6 +255,9 @@
     <t>Book_DefaultBook</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_DefaultBook.DA_WeaponFX_Book_DefaultBook",BasicAttackTag=(TagName="FX.Weapon.Book.DefaultBook.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.DefaultBook.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.DefaultBook.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.DefaultBook.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Book/Book_DefaultBook/SKM_Book_DefaultBook.SKM_Book_DefaultBook</t>
   </si>
   <si>
@@ -228,13 +267,19 @@
     <t>Book_Dictionary</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_Dictionary.DA_WeaponFX_Book_Dictionary",BasicAttackTag=(TagName="FX.Weapon.Book.Dictionary.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.Dictionary.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.Dictionary.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.Dictionary.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Book/Book_Dictionary/SKM_Book_Dictionary.SKM_Book_Dictionary</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_12011_Dictionary.Icon_Book_12011_Dictionary</t>
   </si>
   <si>
-    <t>Book_Event_01</t>
+    <t>Book_EventBook</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_EventBook.DA_WeaponFX_Book_EventBook",BasicAttackTag=(TagName="FX.Weapon.Book.EventBook.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.EventBook.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.EventBook.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.EventBook.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Book/Book_Event_01/SKM_Book_Event_01.SKM_Book_Event_01</t>
@@ -246,6 +291,9 @@
     <t>Book_FlawlessPlaying</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_FlawlessPlaying.DA_WeaponFX_Book_FlawlessPlaying",BasicAttackTag=(TagName="FX.Weapon.Book.FlawlessPlaying.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.FlawlessPlaying.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.FlawlessPlaying.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.FlawlessPlaying.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Book/Book_FlawlessPlaying/SKM_Book_FlawlessPlaying1.SKM_Book_FlawlessPlaying1</t>
   </si>
   <si>
@@ -255,6 +303,9 @@
     <t>Book_HologramHud</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_HologramHud.DA_WeaponFX_Book_HologramHud",BasicAttackTag=(TagName="FX.Weapon.Book.HologramHud.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.HologramHud.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.HologramHud.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.HologramHud.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Book/Book_HologramHud/SKM_Book_HologramHud1.SKM_Book_HologramHud1</t>
   </si>
   <si>
@@ -264,6 +315,9 @@
     <t>Book_MementoMori</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_MementoMori.DA_WeaponFX_Book_MementoMori",BasicAttackTag=(TagName="FX.Weapon.Book.MementoMori.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.MementoMori.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.MementoMori.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.MementoMori.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Book/Book_Mementomori/SKM_Book_MementoMori1.SKM_Book_MementoMori1</t>
   </si>
   <si>
@@ -273,6 +327,9 @@
     <t>Book_PerfectHarmony</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_PerfectHarmony.DA_WeaponFX_Book_PerfectHarmony",BasicAttackTag=(TagName="FX.Weapon.Book.PerfectHarmony.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.PerfectHarmony.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.PerfectHarmony.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.PerfectHarmony.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Book/Book_PerfectHarmony/SKM_Book_PerfectHarmony.SKM_Book_PerfectHarmony</t>
   </si>
   <si>
@@ -288,6 +345,9 @@
     <t>Gun</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_BlackBeard.DA_WeaponFX_Gun_BlackBeard",BasicAttackTag=(TagName="FX.Weapon.Gun.BlackBeard.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.BlackBeard.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.BlackBeard.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.BlackBeard.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Gun/BlackBeard/SKM_Gun_Blackbeard_Scaled.SKM_Gun_Blackbeard_Scaled</t>
   </si>
   <si>
@@ -315,13 +375,19 @@
     <t>Gun_Demonia</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_Demonia.DA_WeaponFX_Gun_Demonia",BasicAttackTag=(TagName="FX.Weapon.Gun.Demonia.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.Demonia.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.Demonia.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.Demonia.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Demonia/SKM_Gun_Demonia.SKM_Gun_Demonia</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_Demonia.Icon_Gun_Demonia</t>
   </si>
   <si>
-    <t>Gun_Event_01</t>
+    <t>Gun_EventGun</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_EventGun.DA_WeaponFX_Gun_EventGun",BasicAttackTag=(TagName="FX.Weapon.Gun.EventGun.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.EventGun.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.EventGun.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.EventGun.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Event_01/SKM_Gun_Event_01.SKM_Gun_Event_01</t>
@@ -333,6 +399,9 @@
     <t>Gun_LovelyCoil</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_Lovelycoil.DA_WeaponFX_Gun_Lovelycoil",BasicAttackTag=(TagName="FX.Weapon.Gun.LovelyCoil.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.LovelyCoil.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.LovelyCoil.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.LovelyCoil.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Lovelycoil/SKM_Gun_Lovelycoil_Scaled.SKM_Gun_Lovelycoil_Scaled</t>
   </si>
   <si>
@@ -342,13 +411,19 @@
     <t>Gun_Mustang</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_Mustang.DA_WeaponFX_Gun_Mustang",BasicAttackTag=(TagName="FX.Weapon.Gun.Mustang.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.Mustang.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.Mustang.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.Mustang.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Mustang/SKM_Gun_Mustang_Scaled.SKM_Gun_Mustang_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13061_Mustang.Icon_Gun_13061_Mustang</t>
   </si>
   <si>
-    <t>Gun_Nail_Gun</t>
+    <t>Gun_NailGun</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_Nailgun.DA_WeaponFX_Gun_Nailgun",BasicAttackTag=(TagName="FX.Weapon.Gun.NailGun.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.NailGun.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.NailGun.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.NailGun.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Gun/DefaultGun/SKM_Gun_DefaultGun.SKM_Gun_DefaultGun</t>
@@ -360,6 +435,9 @@
     <t>Gun_PayBack</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_Payback.DA_WeaponFX_Gun_PayBack",BasicAttackTag=(TagName="FX.Weapon.Gun.PayBack.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.PayBack.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.PayBack.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.PayBack.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Payback/SKM_Gun_Payback_Scaled.SKM_Gun_Payback_Scaled</t>
   </si>
   <si>
@@ -369,6 +447,9 @@
     <t>Gun_Smithers</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_Smithers.DA_WeaponFX_Gun_Smithers",BasicAttackTag=(TagName="FX.Weapon.Gun.Smithers.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.Smithers.BasicAttackHit"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.Smithers.Skill"),SkillHitTag=(TagName="FX.Weapon.Gun.Smithers.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Smithers/SKM_Gun_Smithers_Scaled.SKM_Gun_Smithers_Scaled</t>
   </si>
   <si>
@@ -381,7 +462,7 @@
     <t>(TagName="Item.Type.Weapon.Range.Staff")</t>
   </si>
   <si>
-    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileSkill.GA_ProjectileSkill_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_BasicAttack.GE_Damage_BasicAttack_C'",ProjectileClass="/Script/Engine.BlueprintGeneratedClass'/Game/Blueprints/Object/Projectile/BP_Bullet.BP_Bullet_C'")</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_Anubis.DA_WeaponFX_Staff_Anubis",BasicAttackTag=(TagName="FX.Weapon.Staff.Anubis.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.Anubis.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.Anubis.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.Anubis.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Staff/Staff_Anubis/SKM_Staff_Anubis.SKM_Staff_Anubis</t>
@@ -390,12 +471,18 @@
     <t>Staff_Binder</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_DefaultStaff.DA_WeaponFX_Staff_DefaultStaff",BasicAttackTag=(TagName="FX.Weapon.Staff.Binder.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.Binder.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.Binder.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.Binder.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Staff/Staff_Binder/SKM_Staff_Binder.SKM_Staff_Binder</t>
   </si>
   <si>
     <t>Staff_DeathMatch</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_Deathmatch.DA_WeaponFX_Staff_Deathmatch",BasicAttackTag=(TagName="FX.Weapon.Staff.DeathMatch.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.DeathMatch.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.DeathMatch.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.DeathMatch.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Staff/Staff_Deathmatch/SKM_Staff_Deathmatch.SKM_Staff_Deathmatch</t>
   </si>
   <si>
@@ -405,6 +492,9 @@
     <t>Staff_Decanter</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_Decanter.DA_WeaponFX_Staff_Decanter",BasicAttackTag=(TagName="FX.Weapon.Staff.Decanter.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.Decanter.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.Decanter.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.Decanter.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Staff/Staff_Decanter/SKM_Staff_Decanter.SKM_Staff_Decanter</t>
   </si>
   <si>
@@ -414,10 +504,16 @@
     <t>Staff_DefaultStaff</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_DefaultStaff.DA_WeaponFX_Staff_DefaultStaff",BasicAttackTag=(TagName="FX.Weapon.Staff.DefaultStaff.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.DefaultStaff.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.DefaultStaff.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.DefaultStaff.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Staff/Staff_DefaultStaff/SKM_Staff_DefaultStaff.SKM_Staff_DefaultStaff</t>
   </si>
   <si>
-    <t>Staff_Event_01</t>
+    <t>Staff_EventStaff</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_EventStaff.DA_WeaponFX_Staff_EventStaff",BasicAttackTag=(TagName="FX.Weapon.Staff.EventStaff.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.EventStaff.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.EventStaff.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.EventStaff.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Staff/Staff_Event_01/SKM_Staff_Event_01.SKM_Staff_Event_01</t>
@@ -429,6 +525,9 @@
     <t>Staff_GazeOfDragon</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_GazeOfDragon.DA_WeaponFX_Staff_GazeOfDragon",BasicAttackTag=(TagName="FX.Weapon.Staff.GazeOfDragon.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.GazeOfDragon.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.GazeOfDragon.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.GazeOfDragon.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Staff/Staff_GazeOfDragon/SKM_Staff_GazeOfDragon.SKM_Staff_GazeOfDragon</t>
   </si>
   <si>
@@ -438,12 +537,18 @@
     <t>Staff_Initiator</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_Initiator.DA_WeaponFX_Staff_Initiator",BasicAttackTag=(TagName="FX.Weapon.Staff.Initiator.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.Initiator.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.Initiator.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.Initiator.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Staff/Staff_Initiator/SKM_Staff_Initiator.SKM_Staff_Initiator</t>
   </si>
   <si>
     <t>Staff_OneStroke</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_OneStroke.DA_WeaponFX_Staff_OneStroke",BasicAttackTag=(TagName="FX.Weapon.Staff.OneStroke.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.OneStroke.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.OneStroke.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.OneStroke.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Staff/Staff_OneStroke/SKM_Staff_OneStroke.SKM_Staff_OneStroke</t>
   </si>
   <si>
@@ -453,12 +558,18 @@
     <t>Staff_OverTheHorizon</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_OverTheHorizon.DA_WeaponFX_Staff_OverTheHorizon",BasicAttackTag=(TagName="FX.Weapon.Staff.OverTheHorizon.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.OverTheHorizon.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.OverTheHorizon.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.OverTheHorizon.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Staff/Staff_OverTheHorizon/SKM_Staff_OverTheHorizon.SKM_Staff_OverTheHorizon</t>
   </si>
   <si>
     <t>Staff_StandUp</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_StandUp.DA_WeaponFX_Staff_StandUp",BasicAttackTag=(TagName="FX.Weapon.Staff.StandUp.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.StandUp.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.StandUp.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.StandUp.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Staff/Staff_StandUp/SKM_Staff_StandUp.SKM_Staff_StandUp</t>
   </si>
   <si>
@@ -468,6 +579,9 @@
     <t>Staff_WinterCane</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_Wintercane.DA_WeaponFX_Staff_Wintercane",BasicAttackTag=(TagName="FX.Weapon.Staff.WinterCane.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.WinterCane.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.WinterCane.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.WinterCane.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Staff/Staff_Wintercane/SKM_Staff_Wintercane.SKM_Staff_Wintercane</t>
   </si>
   <si>
@@ -480,6 +594,9 @@
     <t>(TagName="Item.Type.Weapon.Melee.Sword")</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_Army.DA_WeaponFX_Sword_Army",BasicAttackTag=(TagName="FX.Weapon.Sword.Army.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.Army.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.Army.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.Army.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_Justice.SKM_Sword_Justice</t>
   </si>
   <si>
@@ -489,6 +606,9 @@
     <t>Sword_BeamSword</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_BeamSword.DA_WeaponFX_Sword_BeamSword",BasicAttackTag=(TagName="FX.Weapon.Sword.BeamSword.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.BeamSword.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.BeamSword.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.BeamSword.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_BeamSword.SKM_Sword_BeamSword</t>
   </si>
   <si>
@@ -498,6 +618,9 @@
     <t>Sword_ButterSlayer</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_Butterslayer.DA_WeaponFX_Sword_Butterslayer",BasicAttackTag=(TagName="FX.Weapon.Sword.ButterSlayer.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.ButterSlayer.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.ButterSlayer.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.ButterSlayer.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_Butterslayer.SKM_Sword_Butterslayer</t>
   </si>
   <si>
@@ -507,13 +630,19 @@
     <t>Sword_ChainSword</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_ChainSword.DA_WeaponFX_Sword_ChainSword",BasicAttackTag=(TagName="FX.Weapon.Sword.ChainSword.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.ChainSword.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.ChainSword.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.ChainSword.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_ChainSword.SKM_Sword_ChainSword</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_ChainSword.Icon_Sword_ChainSword</t>
   </si>
   <si>
-    <t>Sword_Event_01</t>
+    <t>Sword_EventSword</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_EventSword.DA_WeaponFX_Sword_EventSword",BasicAttackTag=(TagName="FX.Weapon.Sword.EventSword.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.EventSword.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.EventSword.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.EventSword.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_Event_01.SKM_Sword_Event_01</t>
@@ -522,7 +651,10 @@
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_Event_01.Icon_Sword_Event_01</t>
   </si>
   <si>
-    <t>Sword_HonetBlade</t>
+    <t>Sword_HornetBlade</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_HornetBlade.DA_WeaponFX_Sword_HornetBlade",BasicAttackTag=(TagName=""),SkillTag=(TagName=""),BasicAttackHitTag=(TagName=""),SkillHitTag=(TagName=""))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_MilkyWay.SKM_Sword_MilkyWay</t>
@@ -534,6 +666,9 @@
     <t>Sword_Maid</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_Maid.DA_WeaponFX_Sword_Maid",BasicAttackTag=(TagName="FX.Weapon.Sword.Maid.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.Maid.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.Maid.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.Maid.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_Ironmaid.SKM_Sword_Ironmaid</t>
   </si>
   <si>
@@ -541,6 +676,9 @@
   </si>
   <si>
     <t>Sword_MilkyWay</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_MilkyWay.DA_WeaponFX_Sword_MilkyWay",BasicAttackTag=(TagName="FX.Weapon.Sword.MilkyWay.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.MilkyWay.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.MilkyWay.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.MilkyWay.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Sword/Carver/SKM_Sword_Carver_Scaled.SKM_Sword_Carver_Scaled</t>
@@ -1560,21 +1698,21 @@
         <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
       </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -1595,21 +1733,21 @@
         <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
       </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -1630,21 +1768,21 @@
         <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
       </c>
       <c r="K5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -1665,21 +1803,21 @@
         <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -1700,21 +1838,21 @@
         <v>16</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J7" t="s">
         <v>19</v>
       </c>
       <c r="K7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -1735,21 +1873,21 @@
         <v>16</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="I8" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
       </c>
       <c r="K8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -1770,21 +1908,21 @@
         <v>16</v>
       </c>
       <c r="H9" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="I9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J9" t="s">
         <v>19</v>
       </c>
       <c r="K9" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -1805,21 +1943,21 @@
         <v>16</v>
       </c>
       <c r="H10" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="I10" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J10" t="s">
         <v>19</v>
       </c>
       <c r="K10" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -1840,21 +1978,21 @@
         <v>16</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="I11" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="J11" t="s">
         <v>19</v>
       </c>
       <c r="K11" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -1875,21 +2013,21 @@
         <v>16</v>
       </c>
       <c r="H12" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="I12" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="J12" t="s">
         <v>19</v>
       </c>
       <c r="K12" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -1898,33 +2036,33 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G13" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H13" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="I13" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="J13" t="s">
         <v>19</v>
       </c>
       <c r="K13" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -1933,103 +2071,103 @@
         <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G14" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H14" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="I14" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="J14" t="s">
         <v>19</v>
       </c>
       <c r="K14" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
         <v>62</v>
       </c>
-      <c r="B15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" t="s">
-        <v>53</v>
-      </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G15" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H15" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="I15" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="J15" t="s">
         <v>19</v>
       </c>
       <c r="K15" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" t="s">
         <v>65</v>
       </c>
-      <c r="B16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" t="s">
-        <v>54</v>
-      </c>
-      <c r="F16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16" t="s">
-        <v>56</v>
-      </c>
       <c r="H16" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="I16" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="J16" t="s">
         <v>19</v>
       </c>
       <c r="K16" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
@@ -2038,33 +2176,33 @@
         <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E17" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G17" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H17" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="I17" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="J17" t="s">
         <v>19</v>
       </c>
       <c r="K17" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
@@ -2073,33 +2211,33 @@
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E18" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G18" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H18" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="I18" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="J18" t="s">
         <v>19</v>
       </c>
       <c r="K18" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
@@ -2108,33 +2246,33 @@
         <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E19" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G19" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H19" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I19" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="J19" t="s">
         <v>19</v>
       </c>
       <c r="K19" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
@@ -2143,33 +2281,33 @@
         <v>12</v>
       </c>
       <c r="D20" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E20" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F20" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G20" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H20" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="I20" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="J20" t="s">
         <v>19</v>
       </c>
       <c r="K20" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
@@ -2178,33 +2316,33 @@
         <v>12</v>
       </c>
       <c r="D21" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E21" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F21" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G21" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H21" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="I21" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="J21" t="s">
         <v>19</v>
       </c>
       <c r="K21" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B22" t="s">
         <v>12</v>
@@ -2213,33 +2351,33 @@
         <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E22" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G22" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H22" t="s">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="I22" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="J22" t="s">
         <v>19</v>
       </c>
       <c r="K22" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
@@ -2248,33 +2386,33 @@
         <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E23" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="F23" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G23" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H23" t="s">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="I23" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="J23" t="s">
         <v>19</v>
       </c>
       <c r="K23" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
@@ -2283,33 +2421,33 @@
         <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E24" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="F24" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="G24" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="H24" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="I24" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="J24" t="s">
         <v>19</v>
       </c>
       <c r="K24" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
@@ -2318,33 +2456,33 @@
         <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E25" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="F25" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G25" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H25" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="I25" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="J25" t="s">
         <v>19</v>
       </c>
       <c r="K25" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
@@ -2353,33 +2491,33 @@
         <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E26" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="F26" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G26" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H26" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="I26" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="J26" t="s">
         <v>19</v>
       </c>
       <c r="K26" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="B27" t="s">
         <v>12</v>
@@ -2388,68 +2526,68 @@
         <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E27" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="F27" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G27" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H27" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="I27" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="J27" t="s">
         <v>19</v>
       </c>
       <c r="K27" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>129</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" t="s">
         <v>106</v>
       </c>
-      <c r="B28" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" t="s">
-        <v>87</v>
-      </c>
       <c r="E28" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="F28" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G28" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H28" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="I28" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="J28" t="s">
         <v>19</v>
       </c>
       <c r="K28" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="B29" t="s">
         <v>12</v>
@@ -2458,33 +2596,33 @@
         <v>12</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E29" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="F29" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G29" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H29" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="I29" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="J29" t="s">
         <v>19</v>
       </c>
       <c r="K29" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
@@ -2493,33 +2631,33 @@
         <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E30" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="F30" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G30" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H30" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="I30" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="J30" t="s">
         <v>19</v>
       </c>
       <c r="K30" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="B31" t="s">
         <v>12</v>
@@ -2528,33 +2666,33 @@
         <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E31" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="F31" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G31" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H31" t="s">
-        <v>17</v>
+        <v>142</v>
       </c>
       <c r="I31" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="J31" t="s">
         <v>19</v>
       </c>
       <c r="K31" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B32" t="s">
         <v>12</v>
@@ -2563,22 +2701,22 @@
         <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="E32" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F32" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="G32" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H32" t="s">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="I32" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="J32" t="s">
         <v>19</v>
@@ -2589,7 +2727,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="B33" t="s">
         <v>12</v>
@@ -2598,22 +2736,22 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="E33" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F33" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G33" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H33" t="s">
-        <v>17</v>
+        <v>150</v>
       </c>
       <c r="I33" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="J33" t="s">
         <v>19</v>
@@ -2624,7 +2762,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
@@ -2633,33 +2771,33 @@
         <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="E34" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F34" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G34" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H34" t="s">
-        <v>17</v>
+        <v>153</v>
       </c>
       <c r="I34" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="J34" t="s">
         <v>19</v>
       </c>
       <c r="K34" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="B35" t="s">
         <v>12</v>
@@ -2668,33 +2806,33 @@
         <v>12</v>
       </c>
       <c r="D35" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="E35" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F35" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G35" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H35" t="s">
-        <v>17</v>
+        <v>157</v>
       </c>
       <c r="I35" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="J35" t="s">
         <v>19</v>
       </c>
       <c r="K35" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
@@ -2703,22 +2841,22 @@
         <v>12</v>
       </c>
       <c r="D36" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="E36" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F36" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G36" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H36" t="s">
-        <v>17</v>
+        <v>161</v>
       </c>
       <c r="I36" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="J36" t="s">
         <v>19</v>
@@ -2729,7 +2867,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="B37" t="s">
         <v>12</v>
@@ -2738,33 +2876,33 @@
         <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="E37" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="F37" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G37" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H37" t="s">
-        <v>17</v>
+        <v>164</v>
       </c>
       <c r="I37" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="J37" t="s">
         <v>19</v>
       </c>
       <c r="K37" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="B38" t="s">
         <v>12</v>
@@ -2773,33 +2911,33 @@
         <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="E38" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F38" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G38" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H38" t="s">
-        <v>17</v>
+        <v>168</v>
       </c>
       <c r="I38" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="J38" t="s">
         <v>19</v>
       </c>
       <c r="K38" t="s">
-        <v>137</v>
+        <v>170</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>138</v>
+        <v>171</v>
       </c>
       <c r="B39" t="s">
         <v>12</v>
@@ -2808,22 +2946,22 @@
         <v>12</v>
       </c>
       <c r="D39" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="E39" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F39" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G39" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H39" t="s">
-        <v>17</v>
+        <v>172</v>
       </c>
       <c r="I39" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
       <c r="J39" t="s">
         <v>19</v>
@@ -2834,7 +2972,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="B40" t="s">
         <v>12</v>
@@ -2843,33 +2981,33 @@
         <v>12</v>
       </c>
       <c r="D40" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="E40" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F40" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G40" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H40" t="s">
-        <v>17</v>
+        <v>175</v>
       </c>
       <c r="I40" t="s">
-        <v>141</v>
+        <v>176</v>
       </c>
       <c r="J40" t="s">
         <v>19</v>
       </c>
       <c r="K40" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="B41" t="s">
         <v>12</v>
@@ -2878,22 +3016,22 @@
         <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="E41" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F41" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G41" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H41" t="s">
-        <v>17</v>
+        <v>179</v>
       </c>
       <c r="I41" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="J41" t="s">
         <v>19</v>
@@ -2904,7 +3042,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="B42" t="s">
         <v>12</v>
@@ -2913,33 +3051,33 @@
         <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="E42" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F42" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G42" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H42" t="s">
-        <v>17</v>
+        <v>182</v>
       </c>
       <c r="I42" t="s">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="J42" t="s">
         <v>19</v>
       </c>
       <c r="K42" t="s">
-        <v>147</v>
+        <v>184</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="B43" t="s">
         <v>12</v>
@@ -2948,33 +3086,33 @@
         <v>12</v>
       </c>
       <c r="D43" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="E43" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F43" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G43" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H43" t="s">
-        <v>17</v>
+        <v>186</v>
       </c>
       <c r="I43" t="s">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="J43" t="s">
         <v>19</v>
       </c>
       <c r="K43" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>151</v>
+        <v>189</v>
       </c>
       <c r="B44" t="s">
         <v>12</v>
@@ -2983,7 +3121,7 @@
         <v>12</v>
       </c>
       <c r="D44" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="E44" t="s">
         <v>14</v>
@@ -2995,21 +3133,21 @@
         <v>16</v>
       </c>
       <c r="H44" t="s">
-        <v>17</v>
+        <v>191</v>
       </c>
       <c r="I44" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
       <c r="J44" t="s">
         <v>19</v>
       </c>
       <c r="K44" t="s">
-        <v>154</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>155</v>
+        <v>194</v>
       </c>
       <c r="B45" t="s">
         <v>12</v>
@@ -3018,7 +3156,7 @@
         <v>12</v>
       </c>
       <c r="D45" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="E45" t="s">
         <v>14</v>
@@ -3030,21 +3168,21 @@
         <v>16</v>
       </c>
       <c r="H45" t="s">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="I45" t="s">
-        <v>156</v>
+        <v>196</v>
       </c>
       <c r="J45" t="s">
         <v>19</v>
       </c>
       <c r="K45" t="s">
-        <v>157</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>158</v>
+        <v>198</v>
       </c>
       <c r="B46" t="s">
         <v>12</v>
@@ -3053,7 +3191,7 @@
         <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="E46" t="s">
         <v>14</v>
@@ -3065,21 +3203,21 @@
         <v>16</v>
       </c>
       <c r="H46" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="I46" t="s">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="J46" t="s">
         <v>19</v>
       </c>
       <c r="K46" t="s">
-        <v>160</v>
+        <v>201</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>161</v>
+        <v>202</v>
       </c>
       <c r="B47" t="s">
         <v>12</v>
@@ -3088,7 +3226,7 @@
         <v>12</v>
       </c>
       <c r="D47" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="E47" t="s">
         <v>14</v>
@@ -3100,21 +3238,21 @@
         <v>16</v>
       </c>
       <c r="H47" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="I47" t="s">
-        <v>162</v>
+        <v>204</v>
       </c>
       <c r="J47" t="s">
         <v>19</v>
       </c>
       <c r="K47" t="s">
-        <v>163</v>
+        <v>205</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>164</v>
+        <v>206</v>
       </c>
       <c r="B48" t="s">
         <v>12</v>
@@ -3123,7 +3261,7 @@
         <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="E48" t="s">
         <v>14</v>
@@ -3135,21 +3273,21 @@
         <v>16</v>
       </c>
       <c r="H48" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I48" t="s">
-        <v>165</v>
+        <v>208</v>
       </c>
       <c r="J48" t="s">
         <v>19</v>
       </c>
       <c r="K48" t="s">
-        <v>166</v>
+        <v>209</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>167</v>
+        <v>210</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
@@ -3158,7 +3296,7 @@
         <v>12</v>
       </c>
       <c r="D49" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="E49" t="s">
         <v>14</v>
@@ -3170,21 +3308,21 @@
         <v>16</v>
       </c>
       <c r="H49" t="s">
-        <v>17</v>
+        <v>211</v>
       </c>
       <c r="I49" t="s">
-        <v>168</v>
+        <v>212</v>
       </c>
       <c r="J49" t="s">
         <v>19</v>
       </c>
       <c r="K49" t="s">
-        <v>169</v>
+        <v>213</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>170</v>
+        <v>214</v>
       </c>
       <c r="B50" t="s">
         <v>12</v>
@@ -3193,7 +3331,7 @@
         <v>12</v>
       </c>
       <c r="D50" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="E50" t="s">
         <v>14</v>
@@ -3205,21 +3343,21 @@
         <v>16</v>
       </c>
       <c r="H50" t="s">
-        <v>17</v>
+        <v>215</v>
       </c>
       <c r="I50" t="s">
-        <v>171</v>
+        <v>216</v>
       </c>
       <c r="J50" t="s">
         <v>19</v>
       </c>
       <c r="K50" t="s">
-        <v>172</v>
+        <v>217</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>173</v>
+        <v>218</v>
       </c>
       <c r="B51" t="s">
         <v>12</v>
@@ -3228,7 +3366,7 @@
         <v>12</v>
       </c>
       <c r="D51" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="E51" t="s">
         <v>14</v>
@@ -3240,16 +3378,16 @@
         <v>16</v>
       </c>
       <c r="H51" t="s">
-        <v>17</v>
+        <v>219</v>
       </c>
       <c r="I51" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
       <c r="J51" t="s">
         <v>19</v>
       </c>
       <c r="K51" t="s">
-        <v>175</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Excel_Masters/WeaponAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/WeaponAssets_Master.xlsx
@@ -9,17 +9,17 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23745" windowHeight="7590"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="10035"/>
   </bookViews>
   <sheets>
-    <sheet name="WeaponAssets_Master" sheetId="1" r:id="rId1"/>
+    <sheet name="WeaponAssets" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="222">
   <si>
     <t>---</t>
   </si>
@@ -42,7 +42,7 @@
     <t>WeaponSkillSetup</t>
   </si>
   <si>
-    <t>ActionFX</t>
+    <t>WeaponFX</t>
   </si>
   <si>
     <t>ItemMesh</t>
@@ -54,319 +54,478 @@
     <t>Icon</t>
   </si>
   <si>
+    <t>Blunt_Cleaner</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>(TagName="Item.Type.Weapon.Melee.Blunt")</t>
+  </si>
+  <si>
+    <t>Melee</t>
+  </si>
+  <si>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaBasicAttack.GA_AreaBasicAttack_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_BasicAttack.GE_Damage_BasicAttack_C'",ProjectileClass=None)</t>
+  </si>
+  <si>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaSkill.GA_AreaSkill_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Skill.GE_Damage_Skill_C'",ProjectileClass=None)</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Cleaner.DA_WeaponFX_Blunt_Cleaner",BasicAttackTag=(TagName="FX.Weapon.Blunt.Cleaner.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Cleaner.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Cleaner.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Cleaner.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Cleaner/SKM_Blunt_Cleaner.SKM_Blunt_Cleaner</t>
+  </si>
+  <si>
+    <t>Socket_Weapon_R</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Cleaner.Icon_Blunt_Cleaner</t>
+  </si>
+  <si>
+    <t>Blunt_DefaultBlunt</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_DefaultBlunt.DA_WeaponFX_Blunt_DefaultBlunt",BasicAttackTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Blunt/Blunt_DefaultBlunt/SKM_Blunt_DefaultBlunt.SKM_Blunt_DefaultBlunt</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Default_Blunt.Icon_Default_Blunt</t>
+  </si>
+  <si>
+    <t>Blunt_DevilBat</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Devilbat.DA_WeaponFX_Blunt_Devilbat",BasicAttackTag=(TagName="FX.Weapon.Blunt.DevilBat.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.DevilBat.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.DevilBat.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.DevilBat.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Devilbat/SKM_Blunt_Devilbat.SKM_Blunt_Devilbat</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_DevilBat.Icon_Blunt_DevilBat</t>
+  </si>
+  <si>
+    <t>Blunt_EventBlunt</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_EventBlunt.DA_WeaponFX_Blunt_EventBlunt",BasicAttackTag=(TagName="FX.Weapon.Blunt.EventBlunt.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.EventBlunt.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.EventBlunt.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.EventBlunt.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Event_01/SKM_Blunt_Event_01.SKM_Blunt_Event_01</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Event_01.Icon_Blunt_Event_01</t>
+  </si>
+  <si>
     <t>Blunt_Merry</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>(TagName="Item.Type.Weapon.Melee.Blunt")</t>
-  </si>
-  <si>
-    <t>Melee</t>
-  </si>
-  <si>
-    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaSkill.GA_AreaSkill_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'",ProjectileClass=None)</t>
-  </si>
-  <si>
-    <t>(ActionFXData=None,BasicAttackTag=(TagName=""),SkillTag=(TagName=""))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Merry/SKM_Blunt_Merry.SKM_Blunt_Merry</t>
-  </si>
-  <si>
-    <t>Socket_Weapon_R</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Merry.DA_WeaponFX_Blunt_Merry",BasicAttackTag=(TagName="FX.Weapon.Blunt.Merry.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Merry.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Merry.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Merry.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Blunt/Merry/SKM_Blunt_Merry.SKM_Blunt_Merry</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Merry.Icon_Blunt_Merry</t>
   </si>
   <si>
-    <t>Blunt_DefaultBlunt</t>
-  </si>
-  <si>
-    <t>(ActionFXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt.DA_WeaponFX_Blunt",BasicAttackTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.Skill"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_DefaultBlunt/SKM_Blunt_DefaultBlunt.SKM_Blunt_DefaultBlunt</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_DefaultBlunt/T_Blunt_DefaultBlunt.T_Blunt_DefaultBlunt</t>
+    <t>Blunt_Noble</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Noble.DA_WeaponFX_Blunt_Noble",BasicAttackTag=(TagName="FX.Weapon.Blunt.Noble.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Noble.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Noble.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Noble.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Blunt/Noble/SKM_Blunt_Nobel_Scaled.SKM_Blunt_Nobel_Scaled</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Nobel.Icon_Blunt_Nobel</t>
+  </si>
+  <si>
+    <t>Blunt_Nurse</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Nurse.DA_WeaponFX_Blunt_Nurse",BasicAttackTag=(TagName="FX.Weapon.Blunt.Nurse.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Nurse.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Nurse.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Nurse.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Nurse/SKM_Blunt_Nurse.SKM_Blunt_Nurse</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Nurse.Icon_Blunt_Nurse</t>
+  </si>
+  <si>
+    <t>Blunt_Outsider</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Outsider.DA_WeaponFX_Blunt_Outsider",BasicAttackTag=(TagName="FX.Weapon.Blunt.Outsider.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Outsider.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Outsider.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Outsider.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Outsider/SKM_Blunt_Outsider.SKM_Blunt_Outsider</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Outsider.Icon_Blunt_Outsider</t>
+  </si>
+  <si>
+    <t>Blunt_TreasureChest</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_TreasureChest.DA_WeaponFX_Blunt_TreasureChest",BasicAttackTag=(TagName="FX.Weapon.Blunt.TreasureChest.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.TreasureChest.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.TreasureChest.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.TreasureChest.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Blunt/Blunt_TreasureChest/SKM_Blunt_TreasureChest.SKM_Blunt_TreasureChest</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_TreasureChest.Icon_Blunt_TreasureChest</t>
+  </si>
+  <si>
+    <t>Blunt_Tuner</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Tuner.DA_WeaponFX_Blunt_Tuner",BasicAttackTag=(TagName="FX.Weapon.Blunt.Tuner.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Tuner.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Tuner.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Tuner.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Tuner/SKM_Blunt_Tuner.SKM_Blunt_Tuner</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Tuner.Icon_Blunt_Tuner</t>
   </si>
   <si>
     <t>Blunt_Wrench</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Wrench.DA_WeaponFX_Blunt_Wrench",BasicAttackTag=(TagName="FX.Weapon.Blunt.Wrench.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Wrench.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Wrench.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Wrench.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Blunt/Blunt_Wrench/SKM_Blunt_Wrench.SKM_Blunt_Wrench</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Wrench.Icon_Blunt_Wrench</t>
   </si>
   <si>
-    <t>Blunt_Cleaner</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Cleaner/SKM_Blunt_Cleaner.SKM_Blunt_Cleaner</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Cleaner.Icon_Blunt_Cleaner</t>
-  </si>
-  <si>
-    <t>Blunt_Noble</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Noble/SKM_Blunt_Noble.SKM_Blunt_Noble</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Noble/T_Blunt_Noble0.T_Blunt_Noble0</t>
-  </si>
-  <si>
-    <t>Blunt_Nurse</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Nurse/SKM_Blunt_Nurse.SKM_Blunt_Nurse</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Nurse/T_Blunt_Nurse.T_Blunt_Nurse</t>
-  </si>
-  <si>
-    <t>Blunt_Tuner</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Tuner/SKM_Blunt_Tuner.SKM_Blunt_Tuner</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Tuner/T_Blunt_Tuner.T_Blunt_Tuner</t>
-  </si>
-  <si>
-    <t>Blunt_DevilBat</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Devilbat/SKM_Blunt_Devilbat.SKM_Blunt_Devilbat</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_DevilBat.Icon_Blunt_DevilBat</t>
-  </si>
-  <si>
-    <t>Blunt_Outsider</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Outsider/SKM_Blunt_Outsider.SKM_Blunt_Outsider</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Outsider/T_Blunt_Outsider.T_Blunt_Outsider</t>
-  </si>
-  <si>
-    <t>Blunt_Event_01</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Event_01/SKM_Blunt_Event_01.SKM_Blunt_Event_01</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Event_01.Icon_Blunt_Event_01</t>
-  </si>
-  <si>
-    <t>Blunt_TreasureChest</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_TreasureChest/SKM_Blunt_TreasureChest.SKM_Blunt_TreasureChest</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_TreasureChest.Icon_Blunt_TreasureChest</t>
+    <t>Book_BookOfRed</t>
+  </si>
+  <si>
+    <t>(TagName="Item.Type.Weapon.Range.Book")</t>
+  </si>
+  <si>
+    <t>Magic</t>
+  </si>
+  <si>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileBasicAttack.GA_ProjectileBasicAttack_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_BasicAttack.GE_Damage_BasicAttack_C'",ProjectileClass=None)</t>
+  </si>
+  <si>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileSkill.GA_ProjectileSkill_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Skill.GE_Damage_Skill_C'",ProjectileClass=None)</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_BookOfRed.DA_WeaponFX_Book_BookOfRed",BasicAttackTag=(TagName="FX.Weapon.Book.BookOfRed.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.BookOfRed.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.BookOfRed.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.BookOfRed.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Book/Book_BookOfRedMage/SKM_Book_BookOfRedMage1.SKM_Book_BookOfRedMage1</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_12021_BookOfRedMage.Icon_Book_12021_BookOfRedMage</t>
+  </si>
+  <si>
+    <t>Book_CookingForDummies</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_CookingForDummies.DA_WeaponFX_Book_CookingForDummies",BasicAttackTag=(TagName="FX.Weapon.Book.CookingForDummies.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.CookingForDummies.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.CookingForDummies.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.CookingForDummies.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Book/Book_CookingForDummies/SKM_Book_CookingForDummies.SKM_Book_CookingForDummies</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_12041_CookingForDummies.Icon_Book_12041_CookingForDummies</t>
+  </si>
+  <si>
+    <t>Book_DeckCase</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_EventBook.DA_WeaponFX_Book_EventBook",BasicAttackTag=(TagName="FX.Weapon.Book.DeckCase.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.DeckCase.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.DeckCase.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.DeckCase.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Book/DeckCase/SKM_Book_DeckCase1.SKM_Book_DeckCase1</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_12061_DeckCase.Icon_Book_12061_DeckCase</t>
   </si>
   <si>
     <t>Book_DefaultBook</t>
   </si>
   <si>
-    <t>(TagName="Item.Type.Weapon.Range.Book")</t>
-  </si>
-  <si>
-    <t>Book</t>
-  </si>
-  <si>
-    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileBasicAttack.GA_ProjectileBasicAttack_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'",ProjectileClass="/Script/CoreUObject.Class'/Script/Paradise.ProjectileSingleTarget'")</t>
-  </si>
-  <si>
-    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileSkill.GA_ProjectileSkill_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'",ProjectileClass="/Script/CoreUObject.Class'/Script/Paradise.ProjectilePiercing'")</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_DefaultBook.DA_WeaponFX_Book_DefaultBook",BasicAttackTag=(TagName="FX.Weapon.Book.DefaultBook.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.DefaultBook.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.DefaultBook.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.DefaultBook.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Book/Book_DefaultBook/SKM_Book_DefaultBook.SKM_Book_DefaultBook</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_DefaultBook/T_Book_DefaultBook.T_Book_DefaultBook</t>
-  </si>
-  <si>
-    <t>Book_CookingForDummies</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_CookingForDummies/SKM_Book_CookingForDummies.SKM_Book_CookingForDummies</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_12041_CookingForDummies.Icon_Book_12041_CookingForDummies</t>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_DefaultBook.Icon_Book_DefaultBook</t>
   </si>
   <si>
     <t>Book_Dictionary</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_Dictionary.DA_WeaponFX_Book_Dictionary",BasicAttackTag=(TagName="FX.Weapon.Book.Dictionary.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.Dictionary.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.Dictionary.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.Dictionary.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Book/Book_Dictionary/SKM_Book_Dictionary.SKM_Book_Dictionary</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_12011_Dictionary.Icon_Book_12011_Dictionary</t>
   </si>
   <si>
-    <t>Book_DeckCase</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_DeckCase/SKM_Book_DeckCase1.SKM_Book_DeckCase1</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_12061_DeckCase.Icon_Book_12061_DeckCase</t>
+    <t>Book_EventBook</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_EventBook.DA_WeaponFX_Book_EventBook",BasicAttackTag=(TagName="FX.Weapon.Book.EventBook.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.EventBook.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.EventBook.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.EventBook.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Book/Book_Event_01/SKM_Book_Event_01.SKM_Book_Event_01</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_Event_01.Icon_Book_Event_01</t>
+  </si>
+  <si>
+    <t>Book_FlawlessPlaying</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_FlawlessPlaying.DA_WeaponFX_Book_FlawlessPlaying",BasicAttackTag=(TagName="FX.Weapon.Book.FlawlessPlaying.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.FlawlessPlaying.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.FlawlessPlaying.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.FlawlessPlaying.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Book/Book_FlawlessPlaying/SKM_Book_FlawlessPlaying1.SKM_Book_FlawlessPlaying1</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_FlawlessPlaying.Icon_Book_FlawlessPlaying</t>
   </si>
   <si>
     <t>Book_HologramHud</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_HologramHud.DA_WeaponFX_Book_HologramHud",BasicAttackTag=(TagName="FX.Weapon.Book.HologramHud.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.HologramHud.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.HologramHud.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.HologramHud.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Book/Book_HologramHud/SKM_Book_HologramHud1.SKM_Book_HologramHud1</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_HologramHud/T_Book_HologramHud.T_Book_HologramHud</t>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_Courier.Icon_Book_Courier</t>
+  </si>
+  <si>
+    <t>Book_MementoMori</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_MementoMori.DA_WeaponFX_Book_MementoMori",BasicAttackTag=(TagName="FX.Weapon.Book.MementoMori.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.MementoMori.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.MementoMori.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.MementoMori.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Book/Book_Mementomori/SKM_Book_MementoMori1.SKM_Book_MementoMori1</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_Hermit.Icon_Book_Hermit</t>
   </si>
   <si>
     <t>Book_PerfectHarmony</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_PerfectHarmony.DA_WeaponFX_Book_PerfectHarmony",BasicAttackTag=(TagName="FX.Weapon.Book.PerfectHarmony.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.PerfectHarmony.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.PerfectHarmony.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.PerfectHarmony.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Book/Book_PerfectHarmony/SKM_Book_PerfectHarmony.SKM_Book_PerfectHarmony</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_PerfectHarmony/T_Book_PerfectHarmony.T_Book_PerfectHarmony</t>
-  </si>
-  <si>
-    <t>Book_BookOfRed</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_BookOfRedMage/SKM_Book_BookOfRedMage1.SKM_Book_BookOfRedMage1</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_12021_BookOfRedMage.Icon_Book_12021_BookOfRedMage</t>
-  </si>
-  <si>
-    <t>Book_MementoMori</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_Mementomori/SKM_Book_MementoMori1.SKM_Book_MementoMori1</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_Mementomori/T_Book_MementoMori.T_Book_MementoMori</t>
-  </si>
-  <si>
-    <t>Book_Event_01</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_Event_01/SKM_Book_Event_01.SKM_Book_Event_01</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_Event_01.Icon_Book_Event_01</t>
-  </si>
-  <si>
-    <t>Book_FlawlessPlaying</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_FlawlessPlaying/SKM_Book_FlawlessPlaying1.SKM_Book_FlawlessPlaying1</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_FlawlessPlaying/T_Book_FlawlessPlaying.T_Book_FlawlessPlaying</t>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_PerfectHarmony.Icon_Book_PerfectHarmony</t>
+  </si>
+  <si>
+    <t>Gun_BlackBeard</t>
+  </si>
+  <si>
+    <t>(TagName="Item.Type.Weapon.Range.Gun")</t>
+  </si>
+  <si>
+    <t>Gun</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_BlackBeard.DA_WeaponFX_Gun_BlackBeard",BasicAttackTag=(TagName="FX.Weapon.Gun.BlackBeard.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.BlackBeard.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.BlackBeard.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.BlackBeard.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Gun/BlackBeard/SKM_Gun_Blackbeard_Scaled.SKM_Gun_Blackbeard_Scaled</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13041_BlackBeard.Icon_Gun_13041_BlackBeard</t>
   </si>
   <si>
     <t>Gun_BlackNose</t>
   </si>
   <si>
-    <t>(TagName="Item.Type.Weapon.Range.Gun")</t>
-  </si>
-  <si>
-    <t>Gun</t>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileBasicAttack.GA_ProjectileBasicAttack_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_BasicAttack.GE_Damage_BasicAttack_C'",ProjectileClass="/Script/Engine.BlueprintGeneratedClass'/Game/Blueprints/Object/Projectile/BP_Bullet.BP_Bullet_C'")</t>
+  </si>
+  <si>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileSkill.GA_ProjectileSkill_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Skill.GE_Damage_Skill_C'",ProjectileClass="/Script/Engine.BlueprintGeneratedClass'/Game/Blueprints/Object/Projectile/BP_Bullet.BP_Bullet_C'")</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_BlackNose.DA_WeaponFX_Gun_BlackNose",BasicAttackTag=(TagName="FX.Weapon.Gun.BlackNose.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.BlackNose.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.BlackNose.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.BlackNose.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Gun/Gun_BlackNose/SKM_Gun_BlackNose.SKM_Gun_BlackNose</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Weapon/Gun/Gun_BlackNose/T_Gun_BlackNose.T_Gun_BlackNose</t>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_BlackNose.Icon_Gun_BlackNose</t>
+  </si>
+  <si>
+    <t>Gun_Demonia</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_Demonia.DA_WeaponFX_Gun_Demonia",BasicAttackTag=(TagName="FX.Weapon.Gun.Demonia.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.Demonia.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.Demonia.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.Demonia.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Demonia/SKM_Gun_Demonia.SKM_Gun_Demonia</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_Demonia.Icon_Gun_Demonia</t>
+  </si>
+  <si>
+    <t>Gun_EventGun</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_EventGun.DA_WeaponFX_Gun_EventGun",BasicAttackTag=(TagName="FX.Weapon.Gun.EventGun.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.EventGun.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.EventGun.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.EventGun.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Event_01/SKM_Gun_Event_01.SKM_Gun_Event_01</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_Event_01.Icon_Gun_Event_01</t>
+  </si>
+  <si>
+    <t>Gun_LovelyCoil</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_Lovelycoil.DA_WeaponFX_Gun_Lovelycoil",BasicAttackTag=(TagName="FX.Weapon.Gun.LovelyCoil.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.LovelyCoil.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.LovelyCoil.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.LovelyCoil.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Lovelycoil/SKM_Gun_Lovelycoil_Scaled.SKM_Gun_Lovelycoil_Scaled</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13051_LovelyCoil.Icon_Gun_13051_LovelyCoil</t>
+  </si>
+  <si>
+    <t>Gun_Mustang</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_Mustang.DA_WeaponFX_Gun_Mustang",BasicAttackTag=(TagName="FX.Weapon.Gun.Mustang.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.Mustang.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.Mustang.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.Mustang.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Mustang/SKM_Gun_Mustang_Scaled.SKM_Gun_Mustang_Scaled</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13061_Mustang.Icon_Gun_13061_Mustang</t>
+  </si>
+  <si>
+    <t>Gun_NailGun</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_Nailgun.DA_WeaponFX_Gun_Nailgun",BasicAttackTag=(TagName="FX.Weapon.Gun.NailGun.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.NailGun.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.NailGun.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.NailGun.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Gun/DefaultGun/SKM_Gun_DefaultGun.SKM_Gun_DefaultGun</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_NailGun.Icon_Gun_NailGun</t>
+  </si>
+  <si>
+    <t>Gun_PayBack</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_Payback.DA_WeaponFX_Gun_PayBack",BasicAttackTag=(TagName="FX.Weapon.Gun.PayBack.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.PayBack.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.PayBack.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.PayBack.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Payback/SKM_Gun_Payback_Scaled.SKM_Gun_Payback_Scaled</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13011_PayBack.Icon_Gun_13011_PayBack</t>
   </si>
   <si>
     <t>Gun_Smithers</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Weapon/Gun/Gun_DefaultGun/SKM_Gun_Smithers.SKM_Gun_Smithers</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_Smithers.DA_WeaponFX_Gun_Smithers",BasicAttackTag=(TagName="FX.Weapon.Gun.Smithers.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.Smithers.BasicAttackHit"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.Smithers.Skill"),SkillHitTag=(TagName="FX.Weapon.Gun.Smithers.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Smithers/SKM_Gun_Smithers_Scaled.SKM_Gun_Smithers_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_Smithers.Icon_Gun_Smithers</t>
   </si>
   <si>
-    <t>Gun_Nail_Gun</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Gun/Gun_DefaultGun/SKM_Gun_Nailgun.SKM_Gun_Nailgun</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_NailGun.Icon_Gun_NailGun</t>
-  </si>
-  <si>
-    <t>Gun_LovelyCoil</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Gun/Gun_DefaultGun/SKM_Gun_Lovelycoil.SKM_Gun_Lovelycoil</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13051_LovelyCoil.Icon_Gun_13051_LovelyCoil</t>
-  </si>
-  <si>
-    <t>Gun_Mustang</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Gun/Gun_DefaultGun/SKM_Gun_Mustang.SKM_Gun_Mustang</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13061_Mustang.Icon_Gun_13061_Mustang</t>
-  </si>
-  <si>
-    <t>Gun_PayBack</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Gun/Gun_DefaultGun/SKM_Gun_Payback.SKM_Gun_Payback</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13011_PayBack.Icon_Gun_13011_PayBack</t>
-  </si>
-  <si>
-    <t>Gun_Demonia</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Gun/Gun_DefaultGun/SKM_Gun_Demonia.SKM_Gun_Demonia</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_Demonia.Icon_Gun_Demonia</t>
-  </si>
-  <si>
-    <t>Gun_Event_01</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Gun/Gun_DefaultGun/SKM_Gun_Event_01.SKM_Gun_Event_01</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_Event_01.Icon_Gun_Event_01</t>
-  </si>
-  <si>
-    <t>Gun_BlackBeard</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Gun/Gun_Blackbeard/SKM_Gun_Blackbeard1.SKM_Gun_Blackbeard1</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13041_BlackBeard.Icon_Gun_13041_BlackBeard</t>
+    <t>Staff_Anubis</t>
+  </si>
+  <si>
+    <t>(TagName="Item.Type.Weapon.Range.Staff")</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_Anubis.DA_WeaponFX_Staff_Anubis",BasicAttackTag=(TagName="FX.Weapon.Staff.Anubis.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.Anubis.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.Anubis.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.Anubis.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Staff/Staff_Anubis/SKM_Staff_Anubis.SKM_Staff_Anubis</t>
+  </si>
+  <si>
+    <t>Staff_Binder</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_DefaultStaff.DA_WeaponFX_Staff_DefaultStaff",BasicAttackTag=(TagName="FX.Weapon.Staff.Binder.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.Binder.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.Binder.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.Binder.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Staff/Staff_Binder/SKM_Staff_Binder.SKM_Staff_Binder</t>
+  </si>
+  <si>
+    <t>Staff_DeathMatch</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_Deathmatch.DA_WeaponFX_Staff_Deathmatch",BasicAttackTag=(TagName="FX.Weapon.Staff.DeathMatch.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.DeathMatch.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.DeathMatch.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.DeathMatch.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Staff/Staff_Deathmatch/SKM_Staff_Deathmatch.SKM_Staff_Deathmatch</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11031_DeathMatch.Icon_Staff_11031_DeathMatch</t>
+  </si>
+  <si>
+    <t>Staff_Decanter</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_Decanter.DA_WeaponFX_Staff_Decanter",BasicAttackTag=(TagName="FX.Weapon.Staff.Decanter.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.Decanter.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.Decanter.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.Decanter.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Staff/Staff_Decanter/SKM_Staff_Decanter.SKM_Staff_Decanter</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11051_Decanter.Icon_Staff_11051_Decanter</t>
+  </si>
+  <si>
+    <t>Staff_DefaultStaff</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_DefaultStaff.DA_WeaponFX_Staff_DefaultStaff",BasicAttackTag=(TagName="FX.Weapon.Staff.DefaultStaff.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.DefaultStaff.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.DefaultStaff.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.DefaultStaff.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Staff/Staff_DefaultStaff/SKM_Staff_DefaultStaff.SKM_Staff_DefaultStaff</t>
+  </si>
+  <si>
+    <t>Staff_EventStaff</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_EventStaff.DA_WeaponFX_Staff_EventStaff",BasicAttackTag=(TagName="FX.Weapon.Staff.EventStaff.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.EventStaff.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.EventStaff.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.EventStaff.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Staff/Staff_Event_01/SKM_Staff_Event_01.SKM_Staff_Event_01</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_Event_01.Icon_Staff_Event_01</t>
   </si>
   <si>
     <t>Staff_GazeOfDragon</t>
   </si>
   <si>
-    <t>(TagName="Item.Type.Weapon.Range.Staff")</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_GazeOfDragon.DA_WeaponFX_Staff_GazeOfDragon",BasicAttackTag=(TagName="FX.Weapon.Staff.GazeOfDragon.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.GazeOfDragon.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.GazeOfDragon.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.GazeOfDragon.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Staff/Staff_GazeOfDragon/SKM_Staff_GazeOfDragon.SKM_Staff_GazeOfDragon</t>
@@ -375,134 +534,157 @@
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_Rogue.Icon_Staff_Rogue</t>
   </si>
   <si>
+    <t>Staff_Initiator</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_Initiator.DA_WeaponFX_Staff_Initiator",BasicAttackTag=(TagName="FX.Weapon.Staff.Initiator.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.Initiator.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.Initiator.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.Initiator.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Staff/Staff_Initiator/SKM_Staff_Initiator.SKM_Staff_Initiator</t>
+  </si>
+  <si>
+    <t>Staff_OneStroke</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_OneStroke.DA_WeaponFX_Staff_OneStroke",BasicAttackTag=(TagName="FX.Weapon.Staff.OneStroke.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.OneStroke.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.OneStroke.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.OneStroke.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Staff/Staff_OneStroke/SKM_Staff_OneStroke.SKM_Staff_OneStroke</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11041_OneStroke.Icon_Staff_11041_OneStroke</t>
+  </si>
+  <si>
+    <t>Staff_OverTheHorizon</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_OverTheHorizon.DA_WeaponFX_Staff_OverTheHorizon",BasicAttackTag=(TagName="FX.Weapon.Staff.OverTheHorizon.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.OverTheHorizon.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.OverTheHorizon.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.OverTheHorizon.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Staff/Staff_OverTheHorizon/SKM_Staff_OverTheHorizon.SKM_Staff_OverTheHorizon</t>
+  </si>
+  <si>
     <t>Staff_StandUp</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Weapon/Staff/Staff_Anubis/SKM_Staff_StandUp.SKM_Staff_StandUp</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_StandUp.DA_WeaponFX_Staff_StandUp",BasicAttackTag=(TagName="FX.Weapon.Staff.StandUp.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.StandUp.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.StandUp.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.StandUp.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Staff/Staff_StandUp/SKM_Staff_StandUp.SKM_Staff_StandUp</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_Bard.Icon_Staff_Bard</t>
   </si>
   <si>
-    <t>Staff_OneStroke</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Staff/Staff_Anubis/SKM_Staff_OneStroke.SKM_Staff_OneStroke</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11041_OneStroke.Icon_Staff_11041_OneStroke</t>
-  </si>
-  <si>
-    <t>Staff_Decanter</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Staff/Staff_Anubis/SKM_Staff_Decanter.SKM_Staff_Decanter</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11051_Decanter.Icon_Staff_11051_Decanter</t>
-  </si>
-  <si>
-    <t>Staff_DeathMatch</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Staff/Staff_Deathmatch/SKM_Staff_Deathmatch.SKM_Staff_Deathmatch</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11031_DeathMatch.Icon_Staff_11031_DeathMatch</t>
-  </si>
-  <si>
     <t>Staff_WinterCane</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Weapon/Staff/Staff_Anubis/SKM_Staff_Wintercane.SKM_Staff_Wintercane</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_Wintercane.DA_WeaponFX_Staff_Wintercane",BasicAttackTag=(TagName="FX.Weapon.Staff.WinterCane.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.WinterCane.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.WinterCane.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.WinterCane.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Staff/Staff_Wintercane/SKM_Staff_Wintercane.SKM_Staff_Wintercane</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11061_WinterCane.Icon_Staff_11061_WinterCane</t>
   </si>
   <si>
-    <t>Staff_Event_01</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Staff/Staff_Anubis/SKM_Staff_Event_01.SKM_Staff_Event_01</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_Event_01.Icon_Staff_Event_01</t>
-  </si>
-  <si>
     <t>Sword_Army</t>
   </si>
   <si>
     <t>(TagName="Item.Type.Weapon.Melee.Sword")</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_Army.DA_WeaponFX_Sword_Army",BasicAttackTag=(TagName="FX.Weapon.Sword.Army.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.Army.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.Army.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.Army.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_Justice.SKM_Sword_Justice</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_Army.Icon_Sword_Army</t>
   </si>
   <si>
+    <t>Sword_BeamSword</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_BeamSword.DA_WeaponFX_Sword_BeamSword",BasicAttackTag=(TagName="FX.Weapon.Sword.BeamSword.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.BeamSword.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.BeamSword.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.BeamSword.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_BeamSword.SKM_Sword_BeamSword</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_BeamSword.Icon_Sword_BeamSword</t>
+  </si>
+  <si>
     <t>Sword_ButterSlayer</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_Butterslayer.DA_WeaponFX_Sword_Butterslayer",BasicAttackTag=(TagName="FX.Weapon.Sword.ButterSlayer.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.ButterSlayer.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.ButterSlayer.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.ButterSlayer.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_Butterslayer.SKM_Sword_Butterslayer</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_ButterSlayer.Icon_Sword_ButterSlayer</t>
   </si>
   <si>
-    <t>Sword_HonetBlade</t>
+    <t>Sword_ChainSword</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_ChainSword.DA_WeaponFX_Sword_ChainSword",BasicAttackTag=(TagName="FX.Weapon.Sword.ChainSword.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.ChainSword.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.ChainSword.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.ChainSword.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_ChainSword.SKM_Sword_ChainSword</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_ChainSword.Icon_Sword_ChainSword</t>
+  </si>
+  <si>
+    <t>Sword_EventSword</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_EventSword.DA_WeaponFX_Sword_EventSword",BasicAttackTag=(TagName="FX.Weapon.Sword.EventSword.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.EventSword.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.EventSword.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.EventSword.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_Event_01.SKM_Sword_Event_01</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_Event_01.Icon_Sword_Event_01</t>
+  </si>
+  <si>
+    <t>Sword_HornetBlade</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_HornetBlade.DA_WeaponFX_Sword_HornetBlade",BasicAttackTag=(TagName=""),SkillTag=(TagName=""),BasicAttackHitTag=(TagName=""),SkillHitTag=(TagName=""))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_MilkyWay.SKM_Sword_MilkyWay</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Weapon/Sword/Sword_HornetBlade/T_Sword_HornetBlade.T_Sword_HornetBlade</t>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_HonetBlade.Icon_Sword_HonetBlade</t>
   </si>
   <si>
     <t>Sword_Maid</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_Maid.DA_WeaponFX_Sword_Maid",BasicAttackTag=(TagName="FX.Weapon.Sword.Maid.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.Maid.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.Maid.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.Maid.SkillHit"))</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_Ironmaid.SKM_Sword_Ironmaid</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_Maid.Icon_Sword_Maid</t>
   </si>
   <si>
-    <t>Sword_BeamSword</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_BeamSword.SKM_Sword_BeamSword</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_BeamSword.Icon_Sword_BeamSword</t>
-  </si>
-  <si>
-    <t>Sword_ChainSword</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_ChainSword.SKM_Sword_ChainSword</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_ChainSword.Icon_Sword_ChainSword</t>
-  </si>
-  <si>
-    <t>Sword_Event_01</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_Event_01.SKM_Sword_Event_01</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_Event_01.Icon_Sword_Event_01</t>
-  </si>
-  <si>
     <t>Sword_MilkyWay</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_MilkyWay.DA_WeaponFX_Sword_MilkyWay",BasicAttackTag=(TagName="FX.Weapon.Sword.MilkyWay.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.MilkyWay.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.MilkyWay.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.MilkyWay.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Sword/Carver/SKM_Sword_Carver_Scaled.SKM_Sword_Carver_Scaled</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_MilkWay.Icon_Sword_MilkWay</t>
-  </si>
-  <si>
-    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaBasicAttack.GA_AreaBasicAttack_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'",ProjectileClass=None)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1420,7 +1602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -1475,27 +1657,27 @@
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -1510,27 +1692,27 @@
         <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -1545,27 +1727,27 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -1580,27 +1762,27 @@
         <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -1615,27 +1797,27 @@
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="I6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -1650,27 +1832,27 @@
         <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="I7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -1685,27 +1867,27 @@
         <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="I8" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K8" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -1720,27 +1902,27 @@
         <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H9" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="I9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="J9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K9" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -1755,27 +1937,27 @@
         <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H10" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="I10" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="J10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K10" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -1790,27 +1972,27 @@
         <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="I11" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="J11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K11" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -1825,27 +2007,27 @@
         <v>14</v>
       </c>
       <c r="F12" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H12" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="I12" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="J12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K12" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -1854,33 +2036,33 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G13" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="I13" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="J13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K13" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -1889,33 +2071,33 @@
         <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G14" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H14" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="I14" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="J14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K14" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
@@ -1924,68 +2106,68 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G15" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H15" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="I15" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="J15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K15" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" t="s">
         <v>64</v>
       </c>
-      <c r="B16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16" t="s">
-        <v>54</v>
-      </c>
       <c r="G16" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="I16" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="J16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K16" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
@@ -1994,33 +2176,33 @@
         <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E17" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F17" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G17" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H17" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="I17" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="J17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K17" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
@@ -2029,33 +2211,33 @@
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E18" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F18" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G18" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H18" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="I18" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="J18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K18" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
@@ -2064,33 +2246,33 @@
         <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E19" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F19" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G19" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H19" t="s">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="I19" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="J19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K19" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
@@ -2099,33 +2281,33 @@
         <v>12</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E20" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F20" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G20" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H20" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="I20" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="J20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K20" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
@@ -2134,33 +2316,33 @@
         <v>12</v>
       </c>
       <c r="D21" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E21" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F21" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G21" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="I21" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="J21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K21" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="B22" t="s">
         <v>12</v>
@@ -2169,33 +2351,33 @@
         <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E22" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F22" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G22" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H22" t="s">
-        <v>16</v>
+        <v>102</v>
       </c>
       <c r="I22" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="J22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K22" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
@@ -2204,33 +2386,33 @@
         <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="E23" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="F23" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G23" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H23" t="s">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="I23" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="J23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K23" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
@@ -2239,33 +2421,33 @@
         <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="E24" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="F24" t="s">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="G24" t="s">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="H24" t="s">
-        <v>16</v>
+        <v>114</v>
       </c>
       <c r="I24" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="J24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K24" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
@@ -2274,33 +2456,33 @@
         <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="E25" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="F25" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G25" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H25" t="s">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="I25" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="J25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K25" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
@@ -2309,33 +2491,33 @@
         <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="E26" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="F26" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G26" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H26" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="I26" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="J26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K26" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="B27" t="s">
         <v>12</v>
@@ -2344,33 +2526,33 @@
         <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="E27" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="F27" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G27" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H27" t="s">
-        <v>16</v>
+        <v>126</v>
       </c>
       <c r="I27" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="J27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K27" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="B28" t="s">
         <v>12</v>
@@ -2379,33 +2561,33 @@
         <v>12</v>
       </c>
       <c r="D28" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="E28" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="F28" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G28" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H28" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="I28" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="J28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K28" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="B29" t="s">
         <v>12</v>
@@ -2414,33 +2596,33 @@
         <v>12</v>
       </c>
       <c r="D29" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="E29" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="F29" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G29" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H29" t="s">
-        <v>16</v>
+        <v>134</v>
       </c>
       <c r="I29" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="J29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K29" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
@@ -2449,33 +2631,33 @@
         <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="E30" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="F30" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G30" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H30" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="I30" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="J30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K30" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="B31" t="s">
         <v>12</v>
@@ -2484,33 +2666,33 @@
         <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="E31" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="F31" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G31" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H31" t="s">
-        <v>16</v>
+        <v>142</v>
       </c>
       <c r="I31" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="J31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K31" t="s">
-        <v>113</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="B32" t="s">
         <v>12</v>
@@ -2519,33 +2701,33 @@
         <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="E32" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F32" t="s">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="G32" t="s">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="H32" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="I32" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="J32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K32" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="B33" t="s">
         <v>12</v>
@@ -2554,33 +2736,33 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="E33" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F33" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G33" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H33" t="s">
-        <v>16</v>
+        <v>150</v>
       </c>
       <c r="I33" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="J33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K33" t="s">
-        <v>120</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
@@ -2589,33 +2771,33 @@
         <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="E34" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F34" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G34" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H34" t="s">
-        <v>16</v>
+        <v>153</v>
       </c>
       <c r="I34" t="s">
-        <v>122</v>
+        <v>154</v>
       </c>
       <c r="J34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K34" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="B35" t="s">
         <v>12</v>
@@ -2624,33 +2806,33 @@
         <v>12</v>
       </c>
       <c r="D35" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="E35" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F35" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G35" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H35" t="s">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="I35" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="J35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K35" t="s">
-        <v>126</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
@@ -2659,33 +2841,33 @@
         <v>12</v>
       </c>
       <c r="D36" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="E36" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F36" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G36" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H36" t="s">
-        <v>16</v>
+        <v>161</v>
       </c>
       <c r="I36" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="J36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K36" t="s">
-        <v>129</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="B37" t="s">
         <v>12</v>
@@ -2694,33 +2876,33 @@
         <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="E37" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F37" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G37" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H37" t="s">
-        <v>16</v>
+        <v>164</v>
       </c>
       <c r="I37" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="J37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K37" t="s">
-        <v>132</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="B38" t="s">
         <v>12</v>
@@ -2729,33 +2911,33 @@
         <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="E38" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="F38" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G38" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H38" t="s">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c r="I38" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="J38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K38" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="B39" t="s">
         <v>12</v>
@@ -2764,33 +2946,33 @@
         <v>12</v>
       </c>
       <c r="D39" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E39" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="F39" t="s">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="G39" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="H39" t="s">
-        <v>16</v>
+        <v>172</v>
       </c>
       <c r="I39" t="s">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="J39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K39" t="s">
-        <v>139</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="B40" t="s">
         <v>12</v>
@@ -2799,33 +2981,33 @@
         <v>12</v>
       </c>
       <c r="D40" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E40" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="F40" t="s">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="G40" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="H40" t="s">
-        <v>16</v>
+        <v>175</v>
       </c>
       <c r="I40" t="s">
-        <v>141</v>
+        <v>176</v>
       </c>
       <c r="J40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K40" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="B41" t="s">
         <v>12</v>
@@ -2834,68 +3016,68 @@
         <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E41" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="F41" t="s">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="G41" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="H41" t="s">
-        <v>16</v>
+        <v>179</v>
       </c>
       <c r="I41" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="J41" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K41" t="s">
-        <v>145</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>181</v>
+      </c>
+      <c r="B42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s">
         <v>146</v>
       </c>
-      <c r="B42" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" t="s">
-        <v>12</v>
-      </c>
-      <c r="D42" t="s">
-        <v>137</v>
-      </c>
       <c r="E42" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="F42" t="s">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="G42" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="H42" t="s">
-        <v>16</v>
+        <v>182</v>
       </c>
       <c r="I42" t="s">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="J42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K42" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="B43" t="s">
         <v>12</v>
@@ -2904,33 +3086,33 @@
         <v>12</v>
       </c>
       <c r="D43" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E43" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="F43" t="s">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="G43" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="H43" t="s">
-        <v>16</v>
+        <v>186</v>
       </c>
       <c r="I43" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="J43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K43" t="s">
-        <v>151</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="B44" t="s">
         <v>12</v>
@@ -2939,33 +3121,33 @@
         <v>12</v>
       </c>
       <c r="D44" t="s">
-        <v>137</v>
+        <v>190</v>
       </c>
       <c r="E44" t="s">
         <v>14</v>
       </c>
       <c r="F44" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H44" t="s">
-        <v>16</v>
+        <v>191</v>
       </c>
       <c r="I44" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
       <c r="J44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K44" t="s">
-        <v>154</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>155</v>
+        <v>194</v>
       </c>
       <c r="B45" t="s">
         <v>12</v>
@@ -2974,33 +3156,33 @@
         <v>12</v>
       </c>
       <c r="D45" t="s">
-        <v>137</v>
+        <v>190</v>
       </c>
       <c r="E45" t="s">
         <v>14</v>
       </c>
       <c r="F45" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H45" t="s">
-        <v>16</v>
+        <v>195</v>
       </c>
       <c r="I45" t="s">
-        <v>156</v>
+        <v>196</v>
       </c>
       <c r="J45" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K45" t="s">
-        <v>157</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>158</v>
+        <v>198</v>
       </c>
       <c r="B46" t="s">
         <v>12</v>
@@ -3009,28 +3191,203 @@
         <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>137</v>
+        <v>190</v>
       </c>
       <c r="E46" t="s">
         <v>14</v>
       </c>
       <c r="F46" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="G46" t="s">
+        <v>16</v>
+      </c>
+      <c r="H46" t="s">
+        <v>199</v>
+      </c>
+      <c r="I46" t="s">
+        <v>200</v>
+      </c>
+      <c r="J46" t="s">
+        <v>19</v>
+      </c>
+      <c r="K46" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>202</v>
+      </c>
+      <c r="B47" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" t="s">
+        <v>190</v>
+      </c>
+      <c r="E47" t="s">
+        <v>14</v>
+      </c>
+      <c r="F47" t="s">
         <v>15</v>
       </c>
-      <c r="H46" t="s">
+      <c r="G47" t="s">
         <v>16</v>
       </c>
-      <c r="I46" t="s">
-        <v>144</v>
-      </c>
-      <c r="J46" t="s">
-        <v>18</v>
-      </c>
-      <c r="K46" t="s">
-        <v>159</v>
+      <c r="H47" t="s">
+        <v>203</v>
+      </c>
+      <c r="I47" t="s">
+        <v>204</v>
+      </c>
+      <c r="J47" t="s">
+        <v>19</v>
+      </c>
+      <c r="K47" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>206</v>
+      </c>
+      <c r="B48" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" t="s">
+        <v>190</v>
+      </c>
+      <c r="E48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F48" t="s">
+        <v>15</v>
+      </c>
+      <c r="G48" t="s">
+        <v>16</v>
+      </c>
+      <c r="H48" t="s">
+        <v>207</v>
+      </c>
+      <c r="I48" t="s">
+        <v>208</v>
+      </c>
+      <c r="J48" t="s">
+        <v>19</v>
+      </c>
+      <c r="K48" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>210</v>
+      </c>
+      <c r="B49" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" t="s">
+        <v>190</v>
+      </c>
+      <c r="E49" t="s">
+        <v>14</v>
+      </c>
+      <c r="F49" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" t="s">
+        <v>16</v>
+      </c>
+      <c r="H49" t="s">
+        <v>211</v>
+      </c>
+      <c r="I49" t="s">
+        <v>212</v>
+      </c>
+      <c r="J49" t="s">
+        <v>19</v>
+      </c>
+      <c r="K49" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>214</v>
+      </c>
+      <c r="B50" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" t="s">
+        <v>190</v>
+      </c>
+      <c r="E50" t="s">
+        <v>14</v>
+      </c>
+      <c r="F50" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" t="s">
+        <v>16</v>
+      </c>
+      <c r="H50" t="s">
+        <v>215</v>
+      </c>
+      <c r="I50" t="s">
+        <v>216</v>
+      </c>
+      <c r="J50" t="s">
+        <v>19</v>
+      </c>
+      <c r="K50" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>218</v>
+      </c>
+      <c r="B51" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" t="s">
+        <v>190</v>
+      </c>
+      <c r="E51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F51" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" t="s">
+        <v>16</v>
+      </c>
+      <c r="H51" t="s">
+        <v>219</v>
+      </c>
+      <c r="I51" t="s">
+        <v>220</v>
+      </c>
+      <c r="J51" t="s">
+        <v>19</v>
+      </c>
+      <c r="K51" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Excel_Masters/WeaponAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/WeaponAssets_Master.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="232">
   <si>
     <t>---</t>
   </si>
@@ -72,10 +72,10 @@
     <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaSkill.GA_AreaSkill_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Skill.GE_Damage_Skill_C'",ProjectileClass=None)</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Cleaner.DA_WeaponFX_Blunt_Cleaner",BasicAttackTag=(TagName="FX.Weapon.Blunt.Cleaner.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Cleaner.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Cleaner.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Cleaner.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Cleaner/SKM_Blunt_Cleaner.SKM_Blunt_Cleaner</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Blunt/DA_WeaponFX_Blunt_Cleaner.DA_WeaponFX_Blunt_Cleaner",BasicAttackTag=(TagName="FX.Weapon.Blunt.Cleaner.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Cleaner.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Cleaner.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Cleaner.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Blunt/Cleaner/SKM_Blunt_Cleaner_Scaled.SKM_Blunt_Cleaner_Scaled</t>
   </si>
   <si>
     <t>Socket_Weapon_R</t>
@@ -87,7 +87,7 @@
     <t>Blunt_DefaultBlunt</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_DefaultBlunt.DA_WeaponFX_Blunt_DefaultBlunt",BasicAttackTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.SkillHit"))</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Blunt/DA_WeaponFX_Blunt_DefaultBlunt.DA_WeaponFX_Blunt_DefaultBlunt",BasicAttackTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Blunt/Blunt_DefaultBlunt/SKM_Blunt_DefaultBlunt.SKM_Blunt_DefaultBlunt</t>
@@ -99,10 +99,10 @@
     <t>Blunt_DevilBat</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Devilbat.DA_WeaponFX_Blunt_Devilbat",BasicAttackTag=(TagName="FX.Weapon.Blunt.DevilBat.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.DevilBat.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.DevilBat.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.DevilBat.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Devilbat/SKM_Blunt_Devilbat.SKM_Blunt_Devilbat</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Blunt/DA_WeaponFX_Blunt_Devilbat.DA_WeaponFX_Blunt_Devilbat",BasicAttackTag=(TagName="FX.Weapon.Blunt.DevilBat.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.DevilBat.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.DevilBat.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.DevilBat.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Blunt/Devilbat/SKM_Blunt_Devilbat_Scaled.SKM_Blunt_Devilbat_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_DevilBat.Icon_Blunt_DevilBat</t>
@@ -111,7 +111,7 @@
     <t>Blunt_EventBlunt</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_EventBlunt.DA_WeaponFX_Blunt_EventBlunt",BasicAttackTag=(TagName="FX.Weapon.Blunt.EventBlunt.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.EventBlunt.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.EventBlunt.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.EventBlunt.SkillHit"))</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Blunt/DA_WeaponFX_Blunt_EventBlunt.DA_WeaponFX_Blunt_EventBlunt",BasicAttackTag=(TagName="FX.Weapon.Blunt.EventBlunt.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.EventBlunt.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.EventBlunt.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.EventBlunt.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Blunt/Blunt_Event_01/SKM_Blunt_Event_01.SKM_Blunt_Event_01</t>
@@ -123,7 +123,7 @@
     <t>Blunt_Merry</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Merry.DA_WeaponFX_Blunt_Merry",BasicAttackTag=(TagName="FX.Weapon.Blunt.Merry.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Merry.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Merry.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Merry.SkillHit"))</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Blunt/DA_WeaponFX_Blunt_Merry.DA_WeaponFX_Blunt_Merry",BasicAttackTag=(TagName="FX.Weapon.Blunt.Merry.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Merry.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Merry.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Merry.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Blunt/Merry/SKM_Blunt_Merry.SKM_Blunt_Merry</t>
@@ -135,7 +135,7 @@
     <t>Blunt_Noble</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Noble.DA_WeaponFX_Blunt_Noble",BasicAttackTag=(TagName="FX.Weapon.Blunt.Noble.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Noble.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Noble.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Noble.SkillHit"))</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Blunt/DA_WeaponFX_Blunt_Noble.DA_WeaponFX_Blunt_Noble",BasicAttackTag=(TagName="FX.Weapon.Blunt.Noble.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Noble.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Noble.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Noble.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Blunt/Noble/SKM_Blunt_Nobel_Scaled.SKM_Blunt_Nobel_Scaled</t>
@@ -147,7 +147,7 @@
     <t>Blunt_Nurse</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Nurse.DA_WeaponFX_Blunt_Nurse",BasicAttackTag=(TagName="FX.Weapon.Blunt.Nurse.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Nurse.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Nurse.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Nurse.SkillHit"))</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Blunt/DA_WeaponFX_Blunt_Nurse.DA_WeaponFX_Blunt_Nurse",BasicAttackTag=(TagName="FX.Weapon.Blunt.Nurse.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Nurse.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Nurse.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Nurse.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Blunt/Blunt_Nurse/SKM_Blunt_Nurse.SKM_Blunt_Nurse</t>
@@ -159,7 +159,7 @@
     <t>Blunt_Outsider</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Outsider.DA_WeaponFX_Blunt_Outsider",BasicAttackTag=(TagName="FX.Weapon.Blunt.Outsider.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Outsider.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Outsider.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Outsider.SkillHit"))</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Blunt/DA_WeaponFX_Blunt_Outsider.DA_WeaponFX_Blunt_Outsider",BasicAttackTag=(TagName="FX.Weapon.Blunt.Outsider.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Outsider.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Outsider.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Outsider.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Blunt/Blunt_Outsider/SKM_Blunt_Outsider.SKM_Blunt_Outsider</t>
@@ -171,10 +171,10 @@
     <t>Blunt_TreasureChest</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_TreasureChest.DA_WeaponFX_Blunt_TreasureChest",BasicAttackTag=(TagName="FX.Weapon.Blunt.TreasureChest.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.TreasureChest.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.TreasureChest.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.TreasureChest.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_TreasureChest/SKM_Blunt_TreasureChest.SKM_Blunt_TreasureChest</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Blunt/DA_WeaponFX_Blunt_TreasureChest.DA_WeaponFX_Blunt_TreasureChest",BasicAttackTag=(TagName="FX.Weapon.Blunt.TreasureChest.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.TreasureChest.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.TreasureChest.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.TreasureChest.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Blunt/TreasureChest/SKM_Blunt_TreasureChest_Scaled.SKM_Blunt_TreasureChest_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_TreasureChest.Icon_Blunt_TreasureChest</t>
@@ -183,10 +183,10 @@
     <t>Blunt_Tuner</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Tuner.DA_WeaponFX_Blunt_Tuner",BasicAttackTag=(TagName="FX.Weapon.Blunt.Tuner.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Tuner.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Tuner.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Tuner.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Tuner/SKM_Blunt_Tuner.SKM_Blunt_Tuner</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Blunt/DA_WeaponFX_Blunt_Tuner.DA_WeaponFX_Blunt_Tuner",BasicAttackTag=(TagName="FX.Weapon.Blunt.Tuner.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Tuner.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Tuner.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Tuner.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Blunt/Tuner/SKM_Blunt_Tuner_Scaled.SKM_Blunt_Tuner_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Tuner.Icon_Blunt_Tuner</t>
@@ -195,10 +195,13 @@
     <t>Blunt_Wrench</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Blunt_Wrench.DA_WeaponFX_Blunt_Wrench",BasicAttackTag=(TagName="FX.Weapon.Blunt.Wrench.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Wrench.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Wrench.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Wrench.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Blunt/Blunt_Wrench/SKM_Blunt_Wrench.SKM_Blunt_Wrench</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Blunt/DA_WeaponFX_Blunt_Wrench.DA_WeaponFX_Blunt_Wrench",BasicAttackTag=(TagName="FX.Weapon.Blunt.Wrench.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Wrench.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Wrench.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Wrench.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Blunt/Wrench/SKM_Blunt_Wrench_Scaled.SKM_Blunt_Wrench_Scaled</t>
+  </si>
+  <si>
+    <t>Socket_Weapon_Book</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Wrench.Icon_Blunt_Wrench</t>
@@ -219,7 +222,7 @@
     <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileSkill.GA_ProjectileSkill_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Skill.GE_Damage_Skill_C'",ProjectileClass=None)</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_BookOfRed.DA_WeaponFX_Book_BookOfRed",BasicAttackTag=(TagName="FX.Weapon.Book.BookOfRed.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.BookOfRed.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.BookOfRed.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.BookOfRed.SkillHit"))</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Book/DA_WeaponFX_Book_BookOfRed.DA_WeaponFX_Book_BookOfRed",BasicAttackTag=(TagName="FX.Weapon.Book.BookOfRed.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.BookOfRed.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.BookOfRed.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.BookOfRed.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Book/Book_BookOfRedMage/SKM_Book_BookOfRedMage1.SKM_Book_BookOfRedMage1</t>
@@ -231,7 +234,7 @@
     <t>Book_CookingForDummies</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_CookingForDummies.DA_WeaponFX_Book_CookingForDummies",BasicAttackTag=(TagName="FX.Weapon.Book.CookingForDummies.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.CookingForDummies.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.CookingForDummies.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.CookingForDummies.SkillHit"))</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Book/DA_WeaponFX_Book_CookingForDummies.DA_WeaponFX_Book_CookingForDummies",BasicAttackTag=(TagName="FX.Weapon.Book.CookingForDummies.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.CookingForDummies.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.CookingForDummies.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.CookingForDummies.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Book/Book_CookingForDummies/SKM_Book_CookingForDummies.SKM_Book_CookingForDummies</t>
@@ -243,10 +246,10 @@
     <t>Book_DeckCase</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_EventBook.DA_WeaponFX_Book_EventBook",BasicAttackTag=(TagName="FX.Weapon.Book.DeckCase.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.DeckCase.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.DeckCase.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.DeckCase.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledWeaponMesh/Book/DeckCase/SKM_Book_DeckCase1.SKM_Book_DeckCase1</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Book/DA_WeaponFX_Book_DeckCase.DA_WeaponFX_Book_DeckCase",BasicAttackTag=(TagName="FX.Weapon.Book.DeckCase.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.DeckCase.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.DeckCase.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.DeckCase.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Book/Book_DeckCase/SKM_Book_DeckCase.SKM_Book_DeckCase</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_12061_DeckCase.Icon_Book_12061_DeckCase</t>
@@ -255,7 +258,7 @@
     <t>Book_DefaultBook</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_DefaultBook.DA_WeaponFX_Book_DefaultBook",BasicAttackTag=(TagName="FX.Weapon.Book.DefaultBook.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.DefaultBook.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.DefaultBook.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.DefaultBook.SkillHit"))</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Book/DA_WeaponFX_Book_DefaultBook.DA_WeaponFX_Book_DefaultBook",BasicAttackTag=(TagName="FX.Weapon.Book.DefaultBook.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.DefaultBook.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.DefaultBook.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.DefaultBook.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Book/Book_DefaultBook/SKM_Book_DefaultBook.SKM_Book_DefaultBook</t>
@@ -267,7 +270,7 @@
     <t>Book_Dictionary</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_Dictionary.DA_WeaponFX_Book_Dictionary",BasicAttackTag=(TagName="FX.Weapon.Book.Dictionary.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.Dictionary.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.Dictionary.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.Dictionary.SkillHit"))</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Book/DA_WeaponFX_Book_Dictionary.DA_WeaponFX_Book_Dictionary",BasicAttackTag=(TagName="FX.Weapon.Book.Dictionary.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.Dictionary.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.Dictionary.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.Dictionary.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Book/Book_Dictionary/SKM_Book_Dictionary.SKM_Book_Dictionary</t>
@@ -279,7 +282,7 @@
     <t>Book_EventBook</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_EventBook.DA_WeaponFX_Book_EventBook",BasicAttackTag=(TagName="FX.Weapon.Book.EventBook.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.EventBook.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.EventBook.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.EventBook.SkillHit"))</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Book/DA_WeaponFX_Book_EventBook.DA_WeaponFX_Book_EventBook",BasicAttackTag=(TagName="FX.Weapon.Book.EventBook.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.EventBook.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.EventBook.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.EventBook.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Book/Book_Event_01/SKM_Book_Event_01.SKM_Book_Event_01</t>
@@ -291,10 +294,10 @@
     <t>Book_FlawlessPlaying</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_FlawlessPlaying.DA_WeaponFX_Book_FlawlessPlaying",BasicAttackTag=(TagName="FX.Weapon.Book.FlawlessPlaying.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.FlawlessPlaying.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.FlawlessPlaying.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.FlawlessPlaying.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_FlawlessPlaying/SKM_Book_FlawlessPlaying1.SKM_Book_FlawlessPlaying1</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Book/DA_WeaponFX_Book_FlawlessPlaying.DA_WeaponFX_Book_FlawlessPlaying",BasicAttackTag=(TagName="FX.Weapon.Book.FlawlessPlaying.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.FlawlessPlaying.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.FlawlessPlaying.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.FlawlessPlaying.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Book/FlawlessPlaying/Book_FlawlessPlaying_Scaled.Book_FlawlessPlaying_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_FlawlessPlaying.Icon_Book_FlawlessPlaying</t>
@@ -303,10 +306,10 @@
     <t>Book_HologramHud</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_HologramHud.DA_WeaponFX_Book_HologramHud",BasicAttackTag=(TagName="FX.Weapon.Book.HologramHud.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.HologramHud.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.HologramHud.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.HologramHud.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_HologramHud/SKM_Book_HologramHud1.SKM_Book_HologramHud1</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Book/DA_WeaponFX_Book_HologramHud.DA_WeaponFX_Book_HologramHud",BasicAttackTag=(TagName="FX.Weapon.Book.HologramHud.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.HologramHud.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.HologramHud.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.HologramHud.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Book/HologramHud/Book_HologramHud_Scaled.Book_HologramHud_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_Courier.Icon_Book_Courier</t>
@@ -315,10 +318,10 @@
     <t>Book_MementoMori</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_MementoMori.DA_WeaponFX_Book_MementoMori",BasicAttackTag=(TagName="FX.Weapon.Book.MementoMori.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.MementoMori.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.MementoMori.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.MementoMori.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_Mementomori/SKM_Book_MementoMori1.SKM_Book_MementoMori1</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Book/DA_WeaponFX_Book_MementoMori.DA_WeaponFX_Book_MementoMori",BasicAttackTag=(TagName="FX.Weapon.Book.MementoMori.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.MementoMori.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.MementoMori.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.MementoMori.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Book/MementoMori/Book_MementoMori_Scaled.Book_MementoMori_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_Hermit.Icon_Book_Hermit</t>
@@ -327,10 +330,10 @@
     <t>Book_PerfectHarmony</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Book_PerfectHarmony.DA_WeaponFX_Book_PerfectHarmony",BasicAttackTag=(TagName="FX.Weapon.Book.PerfectHarmony.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.PerfectHarmony.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.PerfectHarmony.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.PerfectHarmony.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_PerfectHarmony/SKM_Book_PerfectHarmony.SKM_Book_PerfectHarmony</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Book/DA_WeaponFX_Book_PerfectHarmony.DA_WeaponFX_Book_PerfectHarmony",BasicAttackTag=(TagName="FX.Weapon.Book.PerfectHarmony.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.PerfectHarmony.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.PerfectHarmony.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.PerfectHarmony.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Book/PerfectHarmony/Book_PerfectHarmony_Scaled.Book_PerfectHarmony_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_PerfectHarmony.Icon_Book_PerfectHarmony</t>
@@ -345,12 +348,15 @@
     <t>Gun</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_BlackBeard.DA_WeaponFX_Gun_BlackBeard",BasicAttackTag=(TagName="FX.Weapon.Gun.BlackBeard.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.BlackBeard.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.BlackBeard.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.BlackBeard.SkillHit"))</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Gun/DA_WeaponFX_Gun_BlackBeard.DA_WeaponFX_Gun_BlackBeard",BasicAttackTag=(TagName="FX.Weapon.Gun.BlackBeard.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.BlackBeard.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.BlackBeard.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.BlackBeard.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Gun/BlackBeard/SKM_Gun_Blackbeard_Scaled.SKM_Gun_Blackbeard_Scaled</t>
   </si>
   <si>
+    <t>Socket_Weapon_Gun</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13041_BlackBeard.Icon_Gun_13041_BlackBeard</t>
   </si>
   <si>
@@ -363,10 +369,10 @@
     <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileSkill.GA_ProjectileSkill_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Skill.GE_Damage_Skill_C'",ProjectileClass="/Script/Engine.BlueprintGeneratedClass'/Game/Blueprints/Object/Projectile/BP_Bullet.BP_Bullet_C'")</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_BlackNose.DA_WeaponFX_Gun_BlackNose",BasicAttackTag=(TagName="FX.Weapon.Gun.BlackNose.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.BlackNose.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.BlackNose.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.BlackNose.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Gun/Gun_BlackNose/SKM_Gun_BlackNose.SKM_Gun_BlackNose</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Gun/DA_WeaponFX_Gun_BlackNose.DA_WeaponFX_Gun_BlackNose",BasicAttackTag=(TagName="FX.Weapon.Gun.BlackNose.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.BlackNose.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.BlackNose.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.BlackNose.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Gun/BlackNose/Gun_BlackNose_Scaled.Gun_BlackNose_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_BlackNose.Icon_Gun_BlackNose</t>
@@ -375,10 +381,10 @@
     <t>Gun_Demonia</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_Demonia.DA_WeaponFX_Gun_Demonia",BasicAttackTag=(TagName="FX.Weapon.Gun.Demonia.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.Demonia.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.Demonia.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.Demonia.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Demonia/SKM_Gun_Demonia.SKM_Gun_Demonia</t>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Demonia.DA_CharFX_Demonia",BasicAttackTag=(TagName="FX.Weapon.Gun.Demonia.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.Demonia.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.Demonia.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.Demonia.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Gun/Gun_DefaultGun/SKM_Gun_Demonia.SKM_Gun_Demonia</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_Demonia.Icon_Gun_Demonia</t>
@@ -387,10 +393,10 @@
     <t>Gun_EventGun</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_EventGun.DA_WeaponFX_Gun_EventGun",BasicAttackTag=(TagName="FX.Weapon.Gun.EventGun.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.EventGun.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.EventGun.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.EventGun.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Event_01/SKM_Gun_Event_01.SKM_Gun_Event_01</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Gun/DA_WeaponFX_Gun_EventGun.DA_WeaponFX_Gun_EventGun",BasicAttackTag=(TagName="FX.Weapon.Gun.EventGun.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.EventGun.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.EventGun.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.EventGun.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Gun/Gun_DefaultGun/SKM_Gun_Event_01.SKM_Gun_Event_01</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_Event_01.Icon_Gun_Event_01</t>
@@ -399,7 +405,7 @@
     <t>Gun_LovelyCoil</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_Lovelycoil.DA_WeaponFX_Gun_Lovelycoil",BasicAttackTag=(TagName="FX.Weapon.Gun.LovelyCoil.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.LovelyCoil.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.LovelyCoil.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.LovelyCoil.SkillHit"))</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Gun/DA_WeaponFX_Gun_Lovelycoil.DA_WeaponFX_Gun_Lovelycoil",BasicAttackTag=(TagName="FX.Weapon.Gun.LovelyCoil.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.LovelyCoil.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.LovelyCoil.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.LovelyCoil.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Lovelycoil/SKM_Gun_Lovelycoil_Scaled.SKM_Gun_Lovelycoil_Scaled</t>
@@ -411,7 +417,7 @@
     <t>Gun_Mustang</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_Mustang.DA_WeaponFX_Gun_Mustang",BasicAttackTag=(TagName="FX.Weapon.Gun.Mustang.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.Mustang.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.Mustang.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.Mustang.SkillHit"))</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Gun/DA_WeaponFX_Gun_Mustang.DA_WeaponFX_Gun_Mustang",BasicAttackTag=(TagName="FX.Weapon.Gun.Mustang.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.Mustang.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.Mustang.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.Mustang.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Mustang/SKM_Gun_Mustang_Scaled.SKM_Gun_Mustang_Scaled</t>
@@ -423,10 +429,10 @@
     <t>Gun_NailGun</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_Nailgun.DA_WeaponFX_Gun_Nailgun",BasicAttackTag=(TagName="FX.Weapon.Gun.NailGun.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.NailGun.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.NailGun.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.NailGun.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledWeaponMesh/Gun/DefaultGun/SKM_Gun_DefaultGun.SKM_Gun_DefaultGun</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Gun/DA_WeaponFX_Gun_Nailgun.DA_WeaponFX_Gun_Nailgun",BasicAttackTag=(TagName="FX.Weapon.Gun.NailGun.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.NailGun.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.NailGun.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.NailGun.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Gun/Gun_DefaultGun/SKM_Gun_Nailgun.SKM_Gun_Nailgun</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_NailGun.Icon_Gun_NailGun</t>
@@ -435,7 +441,7 @@
     <t>Gun_PayBack</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_Payback.DA_WeaponFX_Gun_PayBack",BasicAttackTag=(TagName="FX.Weapon.Gun.PayBack.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.PayBack.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.PayBack.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.PayBack.SkillHit"))</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Gun/DA_WeaponFX_Gun_Payback.DA_WeaponFX_Gun_Payback",BasicAttackTag=(TagName="FX.Weapon.Gun.PayBack.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.PayBack.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.PayBack.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.PayBack.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Payback/SKM_Gun_Payback_Scaled.SKM_Gun_Payback_Scaled</t>
@@ -447,7 +453,7 @@
     <t>Gun_Smithers</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Gun_Smithers.DA_WeaponFX_Gun_Smithers",BasicAttackTag=(TagName="FX.Weapon.Gun.Smithers.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.Smithers.BasicAttackHit"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.Smithers.Skill"),SkillHitTag=(TagName="FX.Weapon.Gun.Smithers.SkillHit"))</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Gun/DA_WeaponFX_Gun_Smithers.DA_WeaponFX_Gun_Smithers",BasicAttackTag=(TagName="FX.Weapon.Gun.Smithers.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.Smithers.BasicAttackHit"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.Smithers.Skill"),SkillHitTag=(TagName="FX.Weapon.Gun.Smithers.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Smithers/SKM_Gun_Smithers_Scaled.SKM_Gun_Smithers_Scaled</t>
@@ -462,28 +468,34 @@
     <t>(TagName="Item.Type.Weapon.Range.Staff")</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_Anubis.DA_WeaponFX_Staff_Anubis",BasicAttackTag=(TagName="FX.Weapon.Staff.Anubis.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.Anubis.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.Anubis.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.Anubis.SkillHit"))</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_Anubis.DA_WeaponFX_Staff_Anubis",BasicAttackTag=(TagName="FX.Weapon.Staff.Anubis.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.Anubis.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.Anubis.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.Anubis.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Staff/Staff_Anubis/SKM_Staff_Anubis.SKM_Staff_Anubis</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Staff_Anubis.Staff_Anubis</t>
+  </si>
+  <si>
     <t>Staff_Binder</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_DefaultStaff.DA_WeaponFX_Staff_DefaultStaff",BasicAttackTag=(TagName="FX.Weapon.Staff.Binder.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.Binder.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.Binder.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.Binder.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Staff/Staff_Binder/SKM_Staff_Binder.SKM_Staff_Binder</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_Binder.DA_WeaponFX_Staff_Binder",BasicAttackTag=(TagName="FX.Weapon.Staff.Binder.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.Binder.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.Binder.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.Binder.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Staff/Binder/SKM_Staff_Binder_Scaled.SKM_Staff_Binder_Scaled</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Staff_Binder.Staff_Binder</t>
   </si>
   <si>
     <t>Staff_DeathMatch</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_Deathmatch.DA_WeaponFX_Staff_Deathmatch",BasicAttackTag=(TagName="FX.Weapon.Staff.DeathMatch.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.DeathMatch.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.DeathMatch.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.DeathMatch.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Staff/Staff_Deathmatch/SKM_Staff_Deathmatch.SKM_Staff_Deathmatch</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_Deathmatch.DA_WeaponFX_Staff_Deathmatch",BasicAttackTag=(TagName="FX.Weapon.Staff.DeathMatch.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.DeathMatch.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.DeathMatch.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.DeathMatch.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Staff/Deathmatch/Staff_Deathmatch_Scaled.Staff_Deathmatch_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11031_DeathMatch.Icon_Staff_11031_DeathMatch</t>
@@ -492,10 +504,10 @@
     <t>Staff_Decanter</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_Decanter.DA_WeaponFX_Staff_Decanter",BasicAttackTag=(TagName="FX.Weapon.Staff.Decanter.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.Decanter.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.Decanter.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.Decanter.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Staff/Staff_Decanter/SKM_Staff_Decanter.SKM_Staff_Decanter</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_Decanter.DA_WeaponFX_Staff_Decanter",BasicAttackTag=(TagName="FX.Weapon.Staff.Decanter.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.Decanter.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.Decanter.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.Decanter.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Staff/Decanter/SKM_Staff_Decanter_Scaled.SKM_Staff_Decanter_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11051_Decanter.Icon_Staff_11051_Decanter</t>
@@ -504,16 +516,19 @@
     <t>Staff_DefaultStaff</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_DefaultStaff.DA_WeaponFX_Staff_DefaultStaff",BasicAttackTag=(TagName="FX.Weapon.Staff.DefaultStaff.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.DefaultStaff.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.DefaultStaff.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.DefaultStaff.SkillHit"))</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_DefaultStaff.DA_WeaponFX_Staff_DefaultStaff",BasicAttackTag=(TagName="FX.Weapon.Staff.DefaultStaff.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.DefaultStaff.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.DefaultStaff.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.DefaultStaff.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Staff/Staff_DefaultStaff/SKM_Staff_DefaultStaff.SKM_Staff_DefaultStaff</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Staff_DefaultStaff.Staff_DefaultStaff</t>
+  </si>
+  <si>
     <t>Staff_EventStaff</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_EventStaff.DA_WeaponFX_Staff_EventStaff",BasicAttackTag=(TagName="FX.Weapon.Staff.EventStaff.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.EventStaff.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.EventStaff.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.EventStaff.SkillHit"))</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_EventStaff.DA_WeaponFX_Staff_EventStaff",BasicAttackTag=(TagName="FX.Weapon.Staff.EventStaff.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.EventStaff.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.EventStaff.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.EventStaff.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Staff/Staff_Event_01/SKM_Staff_Event_01.SKM_Staff_Event_01</t>
@@ -525,10 +540,10 @@
     <t>Staff_GazeOfDragon</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_GazeOfDragon.DA_WeaponFX_Staff_GazeOfDragon",BasicAttackTag=(TagName="FX.Weapon.Staff.GazeOfDragon.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.GazeOfDragon.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.GazeOfDragon.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.GazeOfDragon.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Staff/Staff_GazeOfDragon/SKM_Staff_GazeOfDragon.SKM_Staff_GazeOfDragon</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_GazeOfDragon.DA_WeaponFX_Staff_GazeOfDragon",BasicAttackTag=(TagName="FX.Weapon.Staff.GazeOfDragon.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.GazeOfDragon.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.GazeOfDragon.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.GazeOfDragon.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Staff/GazeOfDragon/Staff_GazeOfDragon_Scaled.Staff_GazeOfDragon_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_Rogue.Icon_Staff_Rogue</t>
@@ -537,19 +552,22 @@
     <t>Staff_Initiator</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_Initiator.DA_WeaponFX_Staff_Initiator",BasicAttackTag=(TagName="FX.Weapon.Staff.Initiator.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.Initiator.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.Initiator.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.Initiator.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Staff/Staff_Initiator/SKM_Staff_Initiator.SKM_Staff_Initiator</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_Initiator.DA_WeaponFX_Staff_Initiator",BasicAttackTag=(TagName="FX.Weapon.Staff.Initiator.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.Initiator.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.Initiator.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.Initiator.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Staff/Initiator/SKM_Staff_Initiator_Scaled.SKM_Staff_Initiator_Scaled</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Staff_Initiator.Staff_Initiator</t>
   </si>
   <si>
     <t>Staff_OneStroke</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_OneStroke.DA_WeaponFX_Staff_OneStroke",BasicAttackTag=(TagName="FX.Weapon.Staff.OneStroke.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.OneStroke.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.OneStroke.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.OneStroke.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Staff/Staff_OneStroke/SKM_Staff_OneStroke.SKM_Staff_OneStroke</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_OneStroke.DA_WeaponFX_Staff_OneStroke",BasicAttackTag=(TagName="FX.Weapon.Staff.OneStroke.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.OneStroke.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.OneStroke.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.OneStroke.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Staff/OneStroke/SKM_Staff_OneStroke_Scaled.SKM_Staff_OneStroke_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11041_OneStroke.Icon_Staff_11041_OneStroke</t>
@@ -558,19 +576,22 @@
     <t>Staff_OverTheHorizon</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_OverTheHorizon.DA_WeaponFX_Staff_OverTheHorizon",BasicAttackTag=(TagName="FX.Weapon.Staff.OverTheHorizon.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.OverTheHorizon.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.OverTheHorizon.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.OverTheHorizon.SkillHit"))</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_OverTheHorizon.DA_WeaponFX_Staff_OverTheHorizon",BasicAttackTag=(TagName="FX.Weapon.Staff.OverTheHorizon.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.OverTheHorizon.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.OverTheHorizon.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.OverTheHorizon.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Staff/Staff_OverTheHorizon/SKM_Staff_OverTheHorizon.SKM_Staff_OverTheHorizon</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Staff_OverTheHorizon.Staff_OverTheHorizon</t>
+  </si>
+  <si>
     <t>Staff_StandUp</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_StandUp.DA_WeaponFX_Staff_StandUp",BasicAttackTag=(TagName="FX.Weapon.Staff.StandUp.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.StandUp.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.StandUp.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.StandUp.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Staff/Staff_StandUp/SKM_Staff_StandUp.SKM_Staff_StandUp</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_StandUp.DA_WeaponFX_Staff_StandUp",BasicAttackTag=(TagName="FX.Weapon.Staff.StandUp.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.StandUp.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.StandUp.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.StandUp.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Staff/StandUp/SKM_Staff_StandUp_Scaled.SKM_Staff_StandUp_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_Bard.Icon_Staff_Bard</t>
@@ -579,10 +600,10 @@
     <t>Staff_WinterCane</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Staff_Wintercane.DA_WeaponFX_Staff_Wintercane",BasicAttackTag=(TagName="FX.Weapon.Staff.WinterCane.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.WinterCane.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.WinterCane.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.WinterCane.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Staff/Staff_Wintercane/SKM_Staff_Wintercane.SKM_Staff_Wintercane</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_Wintercane.DA_WeaponFX_Staff_Wintercane",BasicAttackTag=(TagName="FX.Weapon.Staff.WinterCane.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.WinterCane.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.WinterCane.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.WinterCane.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Staff/Wintercane/SKM_Staff_Wintercane_Scaled.SKM_Staff_Wintercane_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11061_WinterCane.Icon_Staff_11061_WinterCane</t>
@@ -594,10 +615,10 @@
     <t>(TagName="Item.Type.Weapon.Melee.Sword")</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_Army.DA_WeaponFX_Sword_Army",BasicAttackTag=(TagName="FX.Weapon.Sword.Army.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.Army.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.Army.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.Army.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_Justice.SKM_Sword_Justice</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Sword/DA_WeaponFX_Sword_Army.DA_WeaponFX_Sword_Army",BasicAttackTag=(TagName="FX.Weapon.Sword.Army.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.Army.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.Army.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.Army.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Sword/Justice/SKM_Sword_Justice_Scaled.SKM_Sword_Justice_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_Army.Icon_Sword_Army</t>
@@ -606,10 +627,10 @@
     <t>Sword_BeamSword</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_BeamSword.DA_WeaponFX_Sword_BeamSword",BasicAttackTag=(TagName="FX.Weapon.Sword.BeamSword.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.BeamSword.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.BeamSword.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.BeamSword.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_BeamSword.SKM_Sword_BeamSword</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Sword/DA_WeaponFX_Sword_BeamSword.DA_WeaponFX_Sword_BeamSword",BasicAttackTag=(TagName="FX.Weapon.Sword.BeamSword.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.BeamSword.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.BeamSword.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.BeamSword.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Sword/BeamSword/SKM_Sword_BeamSword_Scaled.SKM_Sword_BeamSword_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_BeamSword.Icon_Sword_BeamSword</t>
@@ -618,10 +639,10 @@
     <t>Sword_ButterSlayer</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_Butterslayer.DA_WeaponFX_Sword_Butterslayer",BasicAttackTag=(TagName="FX.Weapon.Sword.ButterSlayer.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.ButterSlayer.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.ButterSlayer.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.ButterSlayer.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_Butterslayer.SKM_Sword_Butterslayer</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Sword/DA_WeaponFX_Sword_Butterslayer.DA_WeaponFX_Sword_Butterslayer",BasicAttackTag=(TagName="FX.Weapon.Sword.ButterSlayer.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.ButterSlayer.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.ButterSlayer.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.ButterSlayer.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Sword/Butterslayer/SKM_Sword_Butterslayer_Scaled.SKM_Sword_Butterslayer_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_ButterSlayer.Icon_Sword_ButterSlayer</t>
@@ -630,10 +651,10 @@
     <t>Sword_ChainSword</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_ChainSword.DA_WeaponFX_Sword_ChainSword",BasicAttackTag=(TagName="FX.Weapon.Sword.ChainSword.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.ChainSword.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.ChainSword.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.ChainSword.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_ChainSword.SKM_Sword_ChainSword</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Sword/DA_WeaponFX_Sword_ChainSword.DA_WeaponFX_Sword_ChainSword",BasicAttackTag=(TagName="FX.Weapon.Sword.ChainSword.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.ChainSword.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.ChainSword.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.ChainSword.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Sword/ChainSword/SKM_Sword_ChainSword_Scaled.SKM_Sword_ChainSword_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_ChainSword.Icon_Sword_ChainSword</t>
@@ -642,10 +663,10 @@
     <t>Sword_EventSword</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_EventSword.DA_WeaponFX_Sword_EventSword",BasicAttackTag=(TagName="FX.Weapon.Sword.EventSword.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.EventSword.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.EventSword.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.EventSword.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_Event_01.SKM_Sword_Event_01</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Sword/DA_WeaponFX_Sword_EventSword.DA_WeaponFX_Sword_EventSword",BasicAttackTag=(TagName="FX.Weapon.Sword.EventSword.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.EventSword.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.EventSword.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.EventSword.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Sword/Sword_Event_01/SKM_Sword_Event_01.SKM_Sword_Event_01</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_Event_01.Icon_Sword_Event_01</t>
@@ -654,10 +675,10 @@
     <t>Sword_HornetBlade</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_HornetBlade.DA_WeaponFX_Sword_HornetBlade",BasicAttackTag=(TagName=""),SkillTag=(TagName=""),BasicAttackHitTag=(TagName=""),SkillHitTag=(TagName=""))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_MilkyWay.SKM_Sword_MilkyWay</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Sword/DA_WeaponFX_Sword_HornetBlade.DA_WeaponFX_Sword_HornetBlade",BasicAttackTag=(TagName="FX.Weapon.Sword.HornetBlade.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.HornetBlade.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.HornetBlade.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.HornetBlade.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Sword/HornetBlade/SKM_Sword_HornetBlade_Scaled.SKM_Sword_HornetBlade_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_HonetBlade.Icon_Sword_HonetBlade</t>
@@ -666,10 +687,10 @@
     <t>Sword_Maid</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_Maid.DA_WeaponFX_Sword_Maid",BasicAttackTag=(TagName="FX.Weapon.Sword.Maid.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.Maid.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.Maid.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.Maid.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Sword/Sword_Kumomatsuru/SKM_Sword_Ironmaid.SKM_Sword_Ironmaid</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Sword/DA_WeaponFX_Sword_Maid.DA_WeaponFX_Sword_Maid",BasicAttackTag=(TagName="FX.Weapon.Sword.Maid.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.Maid.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.Maid.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.Maid.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledWeaponMesh/Sword/Ironmaid/SKM_Sword_Ironmaid_Scaled.SKM_Sword_Ironmaid_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_Maid.Icon_Sword_Maid</t>
@@ -678,13 +699,25 @@
     <t>Sword_MilkyWay</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/DA_WeaponFX_Sword_MilkyWay.DA_WeaponFX_Sword_MilkyWay",BasicAttackTag=(TagName="FX.Weapon.Sword.MilkyWay.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.MilkyWay.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.MilkyWay.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.MilkyWay.SkillHit"))</t>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Sword/DA_WeaponFX_Sword_MilkyWay.DA_WeaponFX_Sword_MilkyWay",BasicAttackTag=(TagName="FX.Weapon.Sword.MilkyWay.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.MilkyWay.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.MilkyWay.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.MilkyWay.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Sword/Carver/SKM_Sword_Carver_Scaled.SKM_Sword_Carver_Scaled</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_MilkWay.Icon_Sword_MilkWay</t>
+  </si>
+  <si>
+    <t>Socket_Weapon_Book</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Socket_Weapon_Book</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Socket_Weapon_R</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1984,7 +2017,7 @@
         <v>55</v>
       </c>
       <c r="J11" t="s">
-        <v>19</v>
+        <v>231</v>
       </c>
       <c r="K11" t="s">
         <v>56</v>
@@ -2019,15 +2052,15 @@
         <v>59</v>
       </c>
       <c r="J12" t="s">
-        <v>19</v>
+        <v>231</v>
       </c>
       <c r="K12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -2036,33 +2069,33 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J13" t="s">
-        <v>19</v>
+        <v>229</v>
       </c>
       <c r="K13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -2071,33 +2104,33 @@
         <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J14" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="K14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
@@ -2106,33 +2139,33 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J15" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="K15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
@@ -2141,33 +2174,33 @@
         <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J16" t="s">
-        <v>19</v>
+        <v>230</v>
       </c>
       <c r="K16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
@@ -2176,33 +2209,33 @@
         <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J17" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="K17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
@@ -2211,33 +2244,33 @@
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J18" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="K18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
@@ -2246,33 +2279,33 @@
         <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J19" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="K19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
@@ -2281,33 +2314,33 @@
         <v>12</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J20" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="K20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
@@ -2316,33 +2349,33 @@
         <v>12</v>
       </c>
       <c r="D21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J21" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="K21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B22" t="s">
         <v>12</v>
@@ -2351,33 +2384,33 @@
         <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H22" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J22" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="K22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
@@ -2386,68 +2419,68 @@
         <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J23" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="K23" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" t="s">
+        <v>107</v>
+      </c>
+      <c r="E24" t="s">
+        <v>108</v>
+      </c>
+      <c r="F24" t="s">
+        <v>114</v>
+      </c>
+      <c r="G24" t="s">
+        <v>115</v>
+      </c>
+      <c r="H24" t="s">
+        <v>116</v>
+      </c>
+      <c r="I24" t="s">
+        <v>117</v>
+      </c>
+      <c r="J24" t="s">
         <v>111</v>
       </c>
-      <c r="B24" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" t="s">
-        <v>106</v>
-      </c>
-      <c r="E24" t="s">
-        <v>107</v>
-      </c>
-      <c r="F24" t="s">
-        <v>112</v>
-      </c>
-      <c r="G24" t="s">
-        <v>113</v>
-      </c>
-      <c r="H24" t="s">
-        <v>114</v>
-      </c>
-      <c r="I24" t="s">
-        <v>115</v>
-      </c>
-      <c r="J24" t="s">
-        <v>19</v>
-      </c>
       <c r="K24" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
@@ -2456,33 +2489,33 @@
         <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G25" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H25" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I25" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J25" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="K25" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
@@ -2491,33 +2524,33 @@
         <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E26" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H26" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I26" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J26" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="K26" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B27" t="s">
         <v>12</v>
@@ -2526,33 +2559,33 @@
         <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E27" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H27" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I27" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J27" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="K27" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B28" t="s">
         <v>12</v>
@@ -2561,33 +2594,33 @@
         <v>12</v>
       </c>
       <c r="D28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H28" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I28" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J28" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="K28" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B29" t="s">
         <v>12</v>
@@ -2596,33 +2629,33 @@
         <v>12</v>
       </c>
       <c r="D29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H29" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I29" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J29" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="K29" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
@@ -2631,33 +2664,33 @@
         <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H30" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I30" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J30" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="K30" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B31" t="s">
         <v>12</v>
@@ -2666,33 +2699,33 @@
         <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F31" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H31" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I31" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J31" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="K31" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B32" t="s">
         <v>12</v>
@@ -2701,33 +2734,33 @@
         <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G32" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H32" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I32" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J32" t="s">
         <v>19</v>
       </c>
       <c r="K32" t="s">
-        <v>12</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B33" t="s">
         <v>12</v>
@@ -2736,33 +2769,33 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G33" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H33" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I33" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J33" t="s">
         <v>19</v>
       </c>
       <c r="K33" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
@@ -2771,33 +2804,33 @@
         <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H34" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I34" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="J34" t="s">
         <v>19</v>
       </c>
       <c r="K34" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B35" t="s">
         <v>12</v>
@@ -2806,33 +2839,33 @@
         <v>12</v>
       </c>
       <c r="D35" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E35" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F35" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H35" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I35" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J35" t="s">
         <v>19</v>
       </c>
       <c r="K35" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
@@ -2841,33 +2874,33 @@
         <v>12</v>
       </c>
       <c r="D36" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F36" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H36" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I36" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J36" t="s">
         <v>19</v>
       </c>
       <c r="K36" t="s">
-        <v>12</v>
+        <v>167</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B37" t="s">
         <v>12</v>
@@ -2876,33 +2909,33 @@
         <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G37" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H37" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="I37" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="J37" t="s">
         <v>19</v>
       </c>
       <c r="K37" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B38" t="s">
         <v>12</v>
@@ -2911,33 +2944,33 @@
         <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E38" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H38" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="I38" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="J38" t="s">
         <v>19</v>
       </c>
       <c r="K38" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B39" t="s">
         <v>12</v>
@@ -2946,33 +2979,33 @@
         <v>12</v>
       </c>
       <c r="D39" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E39" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F39" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G39" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H39" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="I39" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="J39" t="s">
         <v>19</v>
       </c>
       <c r="K39" t="s">
-        <v>12</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B40" t="s">
         <v>12</v>
@@ -2981,33 +3014,33 @@
         <v>12</v>
       </c>
       <c r="D40" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E40" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F40" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H40" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="I40" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="J40" t="s">
         <v>19</v>
       </c>
       <c r="K40" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B41" t="s">
         <v>12</v>
@@ -3016,33 +3049,33 @@
         <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F41" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G41" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H41" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="I41" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="J41" t="s">
         <v>19</v>
       </c>
       <c r="K41" t="s">
-        <v>12</v>
+        <v>187</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B42" t="s">
         <v>12</v>
@@ -3051,33 +3084,33 @@
         <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E42" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F42" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G42" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H42" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="I42" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="J42" t="s">
         <v>19</v>
       </c>
       <c r="K42" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B43" t="s">
         <v>12</v>
@@ -3086,33 +3119,33 @@
         <v>12</v>
       </c>
       <c r="D43" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G43" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H43" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="I43" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="J43" t="s">
         <v>19</v>
       </c>
       <c r="K43" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B44" t="s">
         <v>12</v>
@@ -3121,7 +3154,7 @@
         <v>12</v>
       </c>
       <c r="D44" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E44" t="s">
         <v>14</v>
@@ -3133,21 +3166,21 @@
         <v>16</v>
       </c>
       <c r="H44" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="I44" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="J44" t="s">
         <v>19</v>
       </c>
       <c r="K44" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B45" t="s">
         <v>12</v>
@@ -3156,7 +3189,7 @@
         <v>12</v>
       </c>
       <c r="D45" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E45" t="s">
         <v>14</v>
@@ -3168,21 +3201,21 @@
         <v>16</v>
       </c>
       <c r="H45" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="I45" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="J45" t="s">
         <v>19</v>
       </c>
       <c r="K45" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B46" t="s">
         <v>12</v>
@@ -3191,7 +3224,7 @@
         <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E46" t="s">
         <v>14</v>
@@ -3203,21 +3236,21 @@
         <v>16</v>
       </c>
       <c r="H46" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I46" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="J46" t="s">
         <v>19</v>
       </c>
       <c r="K46" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B47" t="s">
         <v>12</v>
@@ -3226,7 +3259,7 @@
         <v>12</v>
       </c>
       <c r="D47" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E47" t="s">
         <v>14</v>
@@ -3238,21 +3271,21 @@
         <v>16</v>
       </c>
       <c r="H47" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="I47" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="J47" t="s">
         <v>19</v>
       </c>
       <c r="K47" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B48" t="s">
         <v>12</v>
@@ -3261,7 +3294,7 @@
         <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E48" t="s">
         <v>14</v>
@@ -3273,21 +3306,21 @@
         <v>16</v>
       </c>
       <c r="H48" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="I48" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="J48" t="s">
         <v>19</v>
       </c>
       <c r="K48" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
@@ -3296,7 +3329,7 @@
         <v>12</v>
       </c>
       <c r="D49" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E49" t="s">
         <v>14</v>
@@ -3308,21 +3341,21 @@
         <v>16</v>
       </c>
       <c r="H49" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="I49" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="J49" t="s">
         <v>19</v>
       </c>
       <c r="K49" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B50" t="s">
         <v>12</v>
@@ -3331,7 +3364,7 @@
         <v>12</v>
       </c>
       <c r="D50" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E50" t="s">
         <v>14</v>
@@ -3343,21 +3376,21 @@
         <v>16</v>
       </c>
       <c r="H50" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="I50" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="J50" t="s">
         <v>19</v>
       </c>
       <c r="K50" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B51" t="s">
         <v>12</v>
@@ -3366,7 +3399,7 @@
         <v>12</v>
       </c>
       <c r="D51" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E51" t="s">
         <v>14</v>
@@ -3378,20 +3411,21 @@
         <v>16</v>
       </c>
       <c r="H51" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="I51" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="J51" t="s">
         <v>19</v>
       </c>
       <c r="K51" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/DesignData/Excel_Masters/WeaponAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/WeaponAssets_Master.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="234">
   <si>
     <t>---</t>
   </si>
@@ -57,7 +57,10 @@
     <t>Blunt_Cleaner</t>
   </si>
   <si>
-    <t>None</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Random_Blunt.Icon_Random_Blunt</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Cleaner.Icon_Blunt_Cleaner</t>
   </si>
   <si>
     <t>(TagName="Item.Type.Weapon.Melee.Blunt")</t>
@@ -81,171 +84,174 @@
     <t>Socket_Weapon_R</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Cleaner.Icon_Blunt_Cleaner</t>
-  </si>
-  <si>
     <t>Blunt_DefaultBlunt</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Default_Blunt.Icon_Default_Blunt</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Blunt/DA_WeaponFX_Blunt_DefaultBlunt.DA_WeaponFX_Blunt_DefaultBlunt",BasicAttackTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.DefaultBlunt.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Blunt/Blunt_DefaultBlunt/SKM_Blunt_DefaultBlunt.SKM_Blunt_DefaultBlunt</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Default_Blunt.Icon_Default_Blunt</t>
-  </si>
-  <si>
     <t>Blunt_DevilBat</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_DevilBat.Icon_Blunt_DevilBat</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Blunt/DA_WeaponFX_Blunt_Devilbat.DA_WeaponFX_Blunt_Devilbat",BasicAttackTag=(TagName="FX.Weapon.Blunt.DevilBat.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.DevilBat.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.DevilBat.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.DevilBat.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Blunt/Devilbat/SKM_Blunt_Devilbat_Scaled.SKM_Blunt_Devilbat_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_DevilBat.Icon_Blunt_DevilBat</t>
-  </si>
-  <si>
     <t>Blunt_EventBlunt</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Event_01.Icon_Blunt_Event_01</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Blunt/DA_WeaponFX_Blunt_EventBlunt.DA_WeaponFX_Blunt_EventBlunt",BasicAttackTag=(TagName="FX.Weapon.Blunt.EventBlunt.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.EventBlunt.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.EventBlunt.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.EventBlunt.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Blunt/Blunt_Event_01/SKM_Blunt_Event_01.SKM_Blunt_Event_01</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Event_01.Icon_Blunt_Event_01</t>
-  </si>
-  <si>
     <t>Blunt_Merry</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Merry.Icon_Blunt_Merry</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Blunt/DA_WeaponFX_Blunt_Merry.DA_WeaponFX_Blunt_Merry",BasicAttackTag=(TagName="FX.Weapon.Blunt.Merry.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Merry.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Merry.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Merry.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Blunt/Merry/SKM_Blunt_Merry.SKM_Blunt_Merry</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Merry.Icon_Blunt_Merry</t>
-  </si>
-  <si>
     <t>Blunt_Noble</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Nobel.Icon_Blunt_Nobel</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Blunt/DA_WeaponFX_Blunt_Noble.DA_WeaponFX_Blunt_Noble",BasicAttackTag=(TagName="FX.Weapon.Blunt.Noble.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Noble.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Noble.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Noble.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Blunt/Noble/SKM_Blunt_Nobel_Scaled.SKM_Blunt_Nobel_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Nobel.Icon_Blunt_Nobel</t>
-  </si>
-  <si>
     <t>Blunt_Nurse</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Nurse.Icon_Blunt_Nurse</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Blunt/DA_WeaponFX_Blunt_Nurse.DA_WeaponFX_Blunt_Nurse",BasicAttackTag=(TagName="FX.Weapon.Blunt.Nurse.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Nurse.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Nurse.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Nurse.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Blunt/Blunt_Nurse/SKM_Blunt_Nurse.SKM_Blunt_Nurse</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Nurse.Icon_Blunt_Nurse</t>
-  </si>
-  <si>
     <t>Blunt_Outsider</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Outsider.Icon_Blunt_Outsider</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Blunt/DA_WeaponFX_Blunt_Outsider.DA_WeaponFX_Blunt_Outsider",BasicAttackTag=(TagName="FX.Weapon.Blunt.Outsider.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Outsider.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Outsider.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Outsider.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Blunt/Blunt_Outsider/SKM_Blunt_Outsider.SKM_Blunt_Outsider</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Outsider.Icon_Blunt_Outsider</t>
-  </si>
-  <si>
     <t>Blunt_TreasureChest</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_TreasureChest.Icon_Blunt_TreasureChest</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Blunt/DA_WeaponFX_Blunt_TreasureChest.DA_WeaponFX_Blunt_TreasureChest",BasicAttackTag=(TagName="FX.Weapon.Blunt.TreasureChest.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.TreasureChest.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.TreasureChest.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.TreasureChest.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Blunt/TreasureChest/SKM_Blunt_TreasureChest_Scaled.SKM_Blunt_TreasureChest_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_TreasureChest.Icon_Blunt_TreasureChest</t>
-  </si>
-  <si>
     <t>Blunt_Tuner</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Tuner.Icon_Blunt_Tuner</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Blunt/DA_WeaponFX_Blunt_Tuner.DA_WeaponFX_Blunt_Tuner",BasicAttackTag=(TagName="FX.Weapon.Blunt.Tuner.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Tuner.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Tuner.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Tuner.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Blunt/Tuner/SKM_Blunt_Tuner_Scaled.SKM_Blunt_Tuner_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Tuner.Icon_Blunt_Tuner</t>
-  </si>
-  <si>
     <t>Blunt_Wrench</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Wrench.Icon_Blunt_Wrench</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Blunt/DA_WeaponFX_Blunt_Wrench.DA_WeaponFX_Blunt_Wrench",BasicAttackTag=(TagName="FX.Weapon.Blunt.Wrench.BasicAttack"),SkillTag=(TagName="FX.Weapon.Blunt.Wrench.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Blunt.Wrench.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Blunt.Wrench.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Blunt/Wrench/SKM_Blunt_Wrench_Scaled.SKM_Blunt_Wrench_Scaled</t>
   </si>
   <si>
+    <t>Book_BookOfRed</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Random_Book.Icon_Random_Book</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_12021_BookOfRedMage.Icon_Book_12021_BookOfRedMage</t>
+  </si>
+  <si>
+    <t>(TagName="Item.Type.Weapon.Range.Book")</t>
+  </si>
+  <si>
+    <t>Magic</t>
+  </si>
+  <si>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileBasicAttack.GA_ProjectileBasicAttack_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_BasicAttack.GE_Damage_BasicAttack_C'",ProjectileClass=None)</t>
+  </si>
+  <si>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileSkill.GA_ProjectileSkill_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Skill.GE_Damage_Skill_C'",ProjectileClass=None)</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Book/DA_WeaponFX_Book_BookOfRed.DA_WeaponFX_Book_BookOfRed",BasicAttackTag=(TagName="FX.Weapon.Book.BookOfRed.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.BookOfRed.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.BookOfRed.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.BookOfRed.SkillHit"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Weapon/Book/Book_BookOfRedMage/SKM_Book_BookOfRedMage1.SKM_Book_BookOfRedMage1</t>
+  </si>
+  <si>
     <t>Socket_Weapon_Book</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Blunt_Wrench.Icon_Blunt_Wrench</t>
-  </si>
-  <si>
-    <t>Book_BookOfRed</t>
-  </si>
-  <si>
-    <t>(TagName="Item.Type.Weapon.Range.Book")</t>
-  </si>
-  <si>
-    <t>Magic</t>
-  </si>
-  <si>
-    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileBasicAttack.GA_ProjectileBasicAttack_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_BasicAttack.GE_Damage_BasicAttack_C'",ProjectileClass=None)</t>
-  </si>
-  <si>
-    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileSkill.GA_ProjectileSkill_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Skill.GE_Damage_Skill_C'",ProjectileClass=None)</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Book/DA_WeaponFX_Book_BookOfRed.DA_WeaponFX_Book_BookOfRed",BasicAttackTag=(TagName="FX.Weapon.Book.BookOfRed.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.BookOfRed.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.BookOfRed.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.BookOfRed.SkillHit"))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Weapon/Book/Book_BookOfRedMage/SKM_Book_BookOfRedMage1.SKM_Book_BookOfRedMage1</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_12021_BookOfRedMage.Icon_Book_12021_BookOfRedMage</t>
-  </si>
-  <si>
     <t>Book_CookingForDummies</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_12041_CookingForDummies.Icon_Book_12041_CookingForDummies</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Book/DA_WeaponFX_Book_CookingForDummies.DA_WeaponFX_Book_CookingForDummies",BasicAttackTag=(TagName="FX.Weapon.Book.CookingForDummies.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.CookingForDummies.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.CookingForDummies.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.CookingForDummies.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Book/Book_CookingForDummies/SKM_Book_CookingForDummies.SKM_Book_CookingForDummies</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_12041_CookingForDummies.Icon_Book_12041_CookingForDummies</t>
-  </si>
-  <si>
     <t>Book_DeckCase</t>
   </si>
   <si>
+    <t>/Game/External_Assets/Weapon/Book/Book_DeckCase/T_Book_DeckCase.T_Book_DeckCase</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Book/DA_WeaponFX_Book_DeckCase.DA_WeaponFX_Book_DeckCase",BasicAttackTag=(TagName="FX.Weapon.Book.DeckCase.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.DeckCase.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.DeckCase.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.DeckCase.SkillHit"))</t>
   </si>
   <si>
@@ -258,90 +264,96 @@
     <t>Book_DefaultBook</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_DefaultBook.Icon_Book_DefaultBook</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Book/DA_WeaponFX_Book_DefaultBook.DA_WeaponFX_Book_DefaultBook",BasicAttackTag=(TagName="FX.Weapon.Book.DefaultBook.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.DefaultBook.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.DefaultBook.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.DefaultBook.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Book/Book_DefaultBook/SKM_Book_DefaultBook.SKM_Book_DefaultBook</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_DefaultBook.Icon_Book_DefaultBook</t>
-  </si>
-  <si>
     <t>Book_Dictionary</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_12011_Dictionary.Icon_Book_12011_Dictionary</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Book/DA_WeaponFX_Book_Dictionary.DA_WeaponFX_Book_Dictionary",BasicAttackTag=(TagName="FX.Weapon.Book.Dictionary.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.Dictionary.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.Dictionary.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.Dictionary.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Book/Book_Dictionary/SKM_Book_Dictionary.SKM_Book_Dictionary</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_12011_Dictionary.Icon_Book_12011_Dictionary</t>
-  </si>
-  <si>
     <t>Book_EventBook</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_Event_01.Icon_Book_Event_01</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Book/DA_WeaponFX_Book_EventBook.DA_WeaponFX_Book_EventBook",BasicAttackTag=(TagName="FX.Weapon.Book.EventBook.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.EventBook.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.EventBook.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.EventBook.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Book/Book_Event_01/SKM_Book_Event_01.SKM_Book_Event_01</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_Event_01.Icon_Book_Event_01</t>
-  </si>
-  <si>
     <t>Book_FlawlessPlaying</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_FlawlessPlaying.Icon_Book_FlawlessPlaying</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Book/DA_WeaponFX_Book_FlawlessPlaying.DA_WeaponFX_Book_FlawlessPlaying",BasicAttackTag=(TagName="FX.Weapon.Book.FlawlessPlaying.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.FlawlessPlaying.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.FlawlessPlaying.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.FlawlessPlaying.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Book/FlawlessPlaying/Book_FlawlessPlaying_Scaled.Book_FlawlessPlaying_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_FlawlessPlaying.Icon_Book_FlawlessPlaying</t>
-  </si>
-  <si>
     <t>Book_HologramHud</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_Courier.Icon_Book_Courier</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Book/DA_WeaponFX_Book_HologramHud.DA_WeaponFX_Book_HologramHud",BasicAttackTag=(TagName="FX.Weapon.Book.HologramHud.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.HologramHud.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.HologramHud.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.HologramHud.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Book/HologramHud/Book_HologramHud_Scaled.Book_HologramHud_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_Courier.Icon_Book_Courier</t>
-  </si>
-  <si>
     <t>Book_MementoMori</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_Hermit.Icon_Book_Hermit</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Book/DA_WeaponFX_Book_MementoMori.DA_WeaponFX_Book_MementoMori",BasicAttackTag=(TagName="FX.Weapon.Book.MementoMori.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.MementoMori.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.MementoMori.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.MementoMori.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Book/MementoMori/Book_MementoMori_Scaled.Book_MementoMori_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_Hermit.Icon_Book_Hermit</t>
-  </si>
-  <si>
     <t>Book_PerfectHarmony</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_PerfectHarmony.Icon_Book_PerfectHarmony</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Book/DA_WeaponFX_Book_PerfectHarmony.DA_WeaponFX_Book_PerfectHarmony",BasicAttackTag=(TagName="FX.Weapon.Book.PerfectHarmony.BasicAttack"),SkillTag=(TagName="FX.Weapon.Book.PerfectHarmony.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Book.PerfectHarmony.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Book.PerfectHarmony.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Book/PerfectHarmony/Book_PerfectHarmony_Scaled.Book_PerfectHarmony_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Book_PerfectHarmony.Icon_Book_PerfectHarmony</t>
-  </si>
-  <si>
     <t>Gun_BlackBeard</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Random_Gun.Icon_Random_Gun</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13041_BlackBeard.Icon_Gun_13041_BlackBeard</t>
+  </si>
+  <si>
     <t>(TagName="Item.Type.Weapon.Range.Gun")</t>
   </si>
   <si>
@@ -357,12 +369,12 @@
     <t>Socket_Weapon_Gun</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13041_BlackBeard.Icon_Gun_13041_BlackBeard</t>
-  </si>
-  <si>
     <t>Gun_BlackNose</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_BlackNose.Icon_Gun_BlackNose</t>
+  </si>
+  <si>
     <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileBasicAttack.GA_ProjectileBasicAttack_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_BasicAttack.GE_Damage_BasicAttack_C'",ProjectileClass="/Script/Engine.BlueprintGeneratedClass'/Game/Blueprints/Object/Projectile/BP_Bullet.BP_Bullet_C'")</t>
   </si>
   <si>
@@ -375,96 +387,99 @@
     <t>/Game/External_Assets/ScaledWeaponMesh/Gun/BlackNose/Gun_BlackNose_Scaled.Gun_BlackNose_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_BlackNose.Icon_Gun_BlackNose</t>
-  </si>
-  <si>
     <t>Gun_Demonia</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_Demonia.Icon_Gun_Demonia</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Demonia.DA_CharFX_Demonia",BasicAttackTag=(TagName="FX.Weapon.Gun.Demonia.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.Demonia.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.Demonia.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.Demonia.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Gun/Gun_DefaultGun/SKM_Gun_Demonia.SKM_Gun_Demonia</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_Demonia.Icon_Gun_Demonia</t>
-  </si>
-  <si>
     <t>Gun_EventGun</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_Event_01.Icon_Gun_Event_01</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Gun/DA_WeaponFX_Gun_EventGun.DA_WeaponFX_Gun_EventGun",BasicAttackTag=(TagName="FX.Weapon.Gun.EventGun.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.EventGun.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.EventGun.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.EventGun.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Gun/Gun_DefaultGun/SKM_Gun_Event_01.SKM_Gun_Event_01</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_Event_01.Icon_Gun_Event_01</t>
-  </si>
-  <si>
     <t>Gun_LovelyCoil</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13051_LovelyCoil.Icon_Gun_13051_LovelyCoil</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Gun/DA_WeaponFX_Gun_Lovelycoil.DA_WeaponFX_Gun_Lovelycoil",BasicAttackTag=(TagName="FX.Weapon.Gun.LovelyCoil.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.LovelyCoil.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.LovelyCoil.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.LovelyCoil.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Lovelycoil/SKM_Gun_Lovelycoil_Scaled.SKM_Gun_Lovelycoil_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13051_LovelyCoil.Icon_Gun_13051_LovelyCoil</t>
-  </si>
-  <si>
     <t>Gun_Mustang</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13061_Mustang.Icon_Gun_13061_Mustang</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Gun/DA_WeaponFX_Gun_Mustang.DA_WeaponFX_Gun_Mustang",BasicAttackTag=(TagName="FX.Weapon.Gun.Mustang.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.Mustang.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.Mustang.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.Mustang.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Mustang/SKM_Gun_Mustang_Scaled.SKM_Gun_Mustang_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13061_Mustang.Icon_Gun_13061_Mustang</t>
-  </si>
-  <si>
     <t>Gun_NailGun</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_NailGun.Icon_Gun_NailGun</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Gun/DA_WeaponFX_Gun_Nailgun.DA_WeaponFX_Gun_Nailgun",BasicAttackTag=(TagName="FX.Weapon.Gun.NailGun.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.NailGun.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.NailGun.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.NailGun.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Gun/Gun_DefaultGun/SKM_Gun_Nailgun.SKM_Gun_Nailgun</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_NailGun.Icon_Gun_NailGun</t>
-  </si>
-  <si>
     <t>Gun_PayBack</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13011_PayBack.Icon_Gun_13011_PayBack</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Gun/DA_WeaponFX_Gun_Payback.DA_WeaponFX_Gun_Payback",BasicAttackTag=(TagName="FX.Weapon.Gun.PayBack.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.PayBack.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.PayBack.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Gun.PayBack.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Payback/SKM_Gun_Payback_Scaled.SKM_Gun_Payback_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_13011_PayBack.Icon_Gun_13011_PayBack</t>
-  </si>
-  <si>
     <t>Gun_Smithers</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_Smithers.Icon_Gun_Smithers</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Gun/DA_WeaponFX_Gun_Smithers.DA_WeaponFX_Gun_Smithers",BasicAttackTag=(TagName="FX.Weapon.Gun.Smithers.BasicAttack"),SkillTag=(TagName="FX.Weapon.Gun.Smithers.BasicAttackHit"),BasicAttackHitTag=(TagName="FX.Weapon.Gun.Smithers.Skill"),SkillHitTag=(TagName="FX.Weapon.Gun.Smithers.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Gun/Smithers/SKM_Gun_Smithers_Scaled.SKM_Gun_Smithers_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Gun_Smithers.Icon_Gun_Smithers</t>
-  </si>
-  <si>
     <t>Staff_Anubis</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Random_Staff.Icon_Random_Staff</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Staff_Anubis.Staff_Anubis</t>
+  </si>
+  <si>
     <t>(TagName="Item.Type.Weapon.Range.Staff")</t>
   </si>
   <si>
@@ -474,144 +489,147 @@
     <t>/Game/External_Assets/Weapon/Staff/Staff_Anubis/SKM_Staff_Anubis.SKM_Staff_Anubis</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Staff_Anubis.Staff_Anubis</t>
-  </si>
-  <si>
     <t>Staff_Binder</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Staff_Binder.Staff_Binder</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_Binder.DA_WeaponFX_Staff_Binder",BasicAttackTag=(TagName="FX.Weapon.Staff.Binder.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.Binder.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.Binder.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.Binder.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Staff/Binder/SKM_Staff_Binder_Scaled.SKM_Staff_Binder_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Staff_Binder.Staff_Binder</t>
-  </si>
-  <si>
     <t>Staff_DeathMatch</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11031_DeathMatch.Icon_Staff_11031_DeathMatch</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_Deathmatch.DA_WeaponFX_Staff_Deathmatch",BasicAttackTag=(TagName="FX.Weapon.Staff.DeathMatch.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.DeathMatch.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.DeathMatch.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.DeathMatch.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Staff/Deathmatch/Staff_Deathmatch_Scaled.Staff_Deathmatch_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11031_DeathMatch.Icon_Staff_11031_DeathMatch</t>
-  </si>
-  <si>
     <t>Staff_Decanter</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11051_Decanter.Icon_Staff_11051_Decanter</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_Decanter.DA_WeaponFX_Staff_Decanter",BasicAttackTag=(TagName="FX.Weapon.Staff.Decanter.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.Decanter.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.Decanter.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.Decanter.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Staff/Decanter/SKM_Staff_Decanter_Scaled.SKM_Staff_Decanter_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11051_Decanter.Icon_Staff_11051_Decanter</t>
-  </si>
-  <si>
     <t>Staff_DefaultStaff</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Staff_DefaultStaff.Staff_DefaultStaff</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_DefaultStaff.DA_WeaponFX_Staff_DefaultStaff",BasicAttackTag=(TagName="FX.Weapon.Staff.DefaultStaff.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.DefaultStaff.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.DefaultStaff.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.DefaultStaff.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Staff/Staff_DefaultStaff/SKM_Staff_DefaultStaff.SKM_Staff_DefaultStaff</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Staff_DefaultStaff.Staff_DefaultStaff</t>
-  </si>
-  <si>
     <t>Staff_EventStaff</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_Event_01.Icon_Staff_Event_01</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_EventStaff.DA_WeaponFX_Staff_EventStaff",BasicAttackTag=(TagName="FX.Weapon.Staff.EventStaff.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.EventStaff.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.EventStaff.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.EventStaff.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Staff/Staff_Event_01/SKM_Staff_Event_01.SKM_Staff_Event_01</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_Event_01.Icon_Staff_Event_01</t>
-  </si>
-  <si>
     <t>Staff_GazeOfDragon</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_Rogue.Icon_Staff_Rogue</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_GazeOfDragon.DA_WeaponFX_Staff_GazeOfDragon",BasicAttackTag=(TagName="FX.Weapon.Staff.GazeOfDragon.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.GazeOfDragon.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.GazeOfDragon.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.GazeOfDragon.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Staff/GazeOfDragon/Staff_GazeOfDragon_Scaled.Staff_GazeOfDragon_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_Rogue.Icon_Staff_Rogue</t>
-  </si>
-  <si>
     <t>Staff_Initiator</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Staff_Initiator.Staff_Initiator</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_Initiator.DA_WeaponFX_Staff_Initiator",BasicAttackTag=(TagName="FX.Weapon.Staff.Initiator.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.Initiator.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.Initiator.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.Initiator.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Staff/Initiator/SKM_Staff_Initiator_Scaled.SKM_Staff_Initiator_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Staff_Initiator.Staff_Initiator</t>
-  </si>
-  <si>
     <t>Staff_OneStroke</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11041_OneStroke.Icon_Staff_11041_OneStroke</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_OneStroke.DA_WeaponFX_Staff_OneStroke",BasicAttackTag=(TagName="FX.Weapon.Staff.OneStroke.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.OneStroke.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.OneStroke.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.OneStroke.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Staff/OneStroke/SKM_Staff_OneStroke_Scaled.SKM_Staff_OneStroke_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11041_OneStroke.Icon_Staff_11041_OneStroke</t>
-  </si>
-  <si>
     <t>Staff_OverTheHorizon</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Staff_OverTheHorizon.Staff_OverTheHorizon</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_OverTheHorizon.DA_WeaponFX_Staff_OverTheHorizon",BasicAttackTag=(TagName="FX.Weapon.Staff.OverTheHorizon.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.OverTheHorizon.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.OverTheHorizon.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.OverTheHorizon.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Staff/Staff_OverTheHorizon/SKM_Staff_OverTheHorizon.SKM_Staff_OverTheHorizon</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Staff_OverTheHorizon.Staff_OverTheHorizon</t>
-  </si>
-  <si>
     <t>Staff_StandUp</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_Bard.Icon_Staff_Bard</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_StandUp.DA_WeaponFX_Staff_StandUp",BasicAttackTag=(TagName="FX.Weapon.Staff.StandUp.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.StandUp.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.StandUp.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.StandUp.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Staff/StandUp/SKM_Staff_StandUp_Scaled.SKM_Staff_StandUp_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_Bard.Icon_Staff_Bard</t>
-  </si>
-  <si>
     <t>Staff_WinterCane</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11061_WinterCane.Icon_Staff_11061_WinterCane</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Staff/DA_WeaponFX_Staff_Wintercane.DA_WeaponFX_Staff_Wintercane",BasicAttackTag=(TagName="FX.Weapon.Staff.WinterCane.BasicAttack"),SkillTag=(TagName="FX.Weapon.Staff.WinterCane.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Staff.WinterCane.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Staff.WinterCane.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Staff/Wintercane/SKM_Staff_Wintercane_Scaled.SKM_Staff_Wintercane_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Staff_11061_WinterCane.Icon_Staff_11061_WinterCane</t>
-  </si>
-  <si>
     <t>Sword_Army</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Random_Sword.Icon_Random_Sword</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_Army.Icon_Sword_Army</t>
+  </si>
+  <si>
     <t>(TagName="Item.Type.Weapon.Melee.Sword")</t>
   </si>
   <si>
@@ -621,103 +639,88 @@
     <t>/Game/External_Assets/ScaledWeaponMesh/Sword/Justice/SKM_Sword_Justice_Scaled.SKM_Sword_Justice_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_Army.Icon_Sword_Army</t>
-  </si>
-  <si>
     <t>Sword_BeamSword</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_BeamSword.Icon_Sword_BeamSword</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Sword/DA_WeaponFX_Sword_BeamSword.DA_WeaponFX_Sword_BeamSword",BasicAttackTag=(TagName="FX.Weapon.Sword.BeamSword.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.BeamSword.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.BeamSword.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.BeamSword.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Sword/BeamSword/SKM_Sword_BeamSword_Scaled.SKM_Sword_BeamSword_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_BeamSword.Icon_Sword_BeamSword</t>
-  </si>
-  <si>
     <t>Sword_ButterSlayer</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_ButterSlayer.Icon_Sword_ButterSlayer</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Sword/DA_WeaponFX_Sword_Butterslayer.DA_WeaponFX_Sword_Butterslayer",BasicAttackTag=(TagName="FX.Weapon.Sword.ButterSlayer.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.ButterSlayer.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.ButterSlayer.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.ButterSlayer.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Sword/Butterslayer/SKM_Sword_Butterslayer_Scaled.SKM_Sword_Butterslayer_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_ButterSlayer.Icon_Sword_ButterSlayer</t>
-  </si>
-  <si>
     <t>Sword_ChainSword</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_ChainSword.Icon_Sword_ChainSword</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Sword/DA_WeaponFX_Sword_ChainSword.DA_WeaponFX_Sword_ChainSword",BasicAttackTag=(TagName="FX.Weapon.Sword.ChainSword.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.ChainSword.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.ChainSword.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.ChainSword.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Sword/ChainSword/SKM_Sword_ChainSword_Scaled.SKM_Sword_ChainSword_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_ChainSword.Icon_Sword_ChainSword</t>
-  </si>
-  <si>
     <t>Sword_EventSword</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_Event_01.Icon_Sword_Event_01</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Sword/DA_WeaponFX_Sword_EventSword.DA_WeaponFX_Sword_EventSword",BasicAttackTag=(TagName="FX.Weapon.Sword.EventSword.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.EventSword.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.EventSword.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.EventSword.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Weapon/Sword/Sword_Event_01/SKM_Sword_Event_01.SKM_Sword_Event_01</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_Event_01.Icon_Sword_Event_01</t>
-  </si>
-  <si>
     <t>Sword_HornetBlade</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_HonetBlade.Icon_Sword_HonetBlade</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Sword/DA_WeaponFX_Sword_HornetBlade.DA_WeaponFX_Sword_HornetBlade",BasicAttackTag=(TagName="FX.Weapon.Sword.HornetBlade.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.HornetBlade.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.HornetBlade.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.HornetBlade.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Sword/HornetBlade/SKM_Sword_HornetBlade_Scaled.SKM_Sword_HornetBlade_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_HonetBlade.Icon_Sword_HonetBlade</t>
-  </si>
-  <si>
     <t>Sword_Maid</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_Maid.Icon_Sword_Maid</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Sword/DA_WeaponFX_Sword_Maid.DA_WeaponFX_Sword_Maid",BasicAttackTag=(TagName="FX.Weapon.Sword.Maid.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.Maid.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.Maid.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.Maid.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Sword/Ironmaid/SKM_Sword_Ironmaid_Scaled.SKM_Sword_Ironmaid_Scaled</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_Maid.Icon_Sword_Maid</t>
-  </si>
-  <si>
     <t>Sword_MilkyWay</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_MilkWay.Icon_Sword_MilkWay</t>
+  </si>
+  <si>
     <t>(FXData="/Game/Data/Assets/WeaponFXAssets/Sword/DA_WeaponFX_Sword_MilkyWay.DA_WeaponFX_Sword_MilkyWay",BasicAttackTag=(TagName="FX.Weapon.Sword.MilkyWay.BasicAttack"),SkillTag=(TagName="FX.Weapon.Sword.MilkyWay.Skill"),BasicAttackHitTag=(TagName="FX.Weapon.Sword.MilkyWay.BasicAttackHit"),SkillHitTag=(TagName="FX.Weapon.Sword.MilkyWay.SkillHit"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/ScaledWeaponMesh/Sword/Carver/SKM_Sword_Carver_Scaled.SKM_Sword_Carver_Scaled</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Sword_MilkWay.Icon_Sword_MilkWay</t>
-  </si>
-  <si>
-    <t>Socket_Weapon_Book</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Socket_Weapon_Book</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Socket_Weapon_R</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1681,31 +1684,31 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
         <v>13</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -1716,31 +1719,31 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
         <v>22</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -1751,31 +1754,31 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s">
         <v>26</v>
-      </c>
-      <c r="I4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -1786,31 +1789,31 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" t="s">
         <v>30</v>
-      </c>
-      <c r="I5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -1821,31 +1824,31 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s">
         <v>34</v>
-      </c>
-      <c r="I6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -1856,31 +1859,31 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" t="s">
         <v>38</v>
-      </c>
-      <c r="I7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -1891,31 +1894,31 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" t="s">
         <v>42</v>
-      </c>
-      <c r="I8" t="s">
-        <v>43</v>
-      </c>
-      <c r="J8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -1926,31 +1929,31 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" t="s">
         <v>46</v>
-      </c>
-      <c r="I9" t="s">
-        <v>47</v>
-      </c>
-      <c r="J9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -1961,31 +1964,31 @@
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" t="s">
         <v>50</v>
-      </c>
-      <c r="I10" t="s">
-        <v>51</v>
-      </c>
-      <c r="J10" t="s">
-        <v>19</v>
-      </c>
-      <c r="K10" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -1996,31 +1999,31 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" t="s">
+        <v>56</v>
+      </c>
+      <c r="J11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" t="s">
         <v>54</v>
-      </c>
-      <c r="I11" t="s">
-        <v>55</v>
-      </c>
-      <c r="J11" t="s">
-        <v>231</v>
-      </c>
-      <c r="K11" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -2031,168 +2034,168 @@
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" t="s">
+        <v>60</v>
+      </c>
+      <c r="J12" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" t="s">
         <v>58</v>
-      </c>
-      <c r="I12" t="s">
-        <v>59</v>
-      </c>
-      <c r="J12" t="s">
-        <v>231</v>
-      </c>
-      <c r="K12" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
         <v>62</v>
       </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" t="s">
+        <v>68</v>
+      </c>
+      <c r="I13" t="s">
+        <v>69</v>
+      </c>
+      <c r="J13" t="s">
+        <v>70</v>
+      </c>
+      <c r="K13" t="s">
         <v>63</v>
-      </c>
-      <c r="E13" t="s">
-        <v>64</v>
-      </c>
-      <c r="F13" t="s">
-        <v>65</v>
-      </c>
-      <c r="G13" t="s">
-        <v>66</v>
-      </c>
-      <c r="H13" t="s">
-        <v>67</v>
-      </c>
-      <c r="I13" t="s">
-        <v>68</v>
-      </c>
-      <c r="J13" t="s">
-        <v>229</v>
-      </c>
-      <c r="K13" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14" t="s">
+        <v>73</v>
+      </c>
+      <c r="I14" t="s">
+        <v>74</v>
+      </c>
+      <c r="J14" t="s">
         <v>70</v>
       </c>
-      <c r="B14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" t="s">
-        <v>64</v>
-      </c>
-      <c r="F14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G14" t="s">
-        <v>66</v>
-      </c>
-      <c r="H14" t="s">
-        <v>71</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="K14" t="s">
         <v>72</v>
-      </c>
-      <c r="J14" t="s">
-        <v>60</v>
-      </c>
-      <c r="K14" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J15" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H16" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I16" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J16" t="s">
-        <v>230</v>
+        <v>70</v>
       </c>
       <c r="K16" t="s">
         <v>81</v>
@@ -2200,34 +2203,34 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H17" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J17" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K17" t="s">
         <v>85</v>
@@ -2235,34 +2238,34 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H18" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I18" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J18" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K18" t="s">
         <v>89</v>
@@ -2270,34 +2273,34 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H19" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I19" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J19" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K19" t="s">
         <v>93</v>
@@ -2305,34 +2308,34 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H20" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I20" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J20" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K20" t="s">
         <v>97</v>
@@ -2340,34 +2343,34 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H21" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J21" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K21" t="s">
         <v>101</v>
@@ -2375,34 +2378,34 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H22" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I22" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J22" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K22" t="s">
         <v>105</v>
@@ -2410,1022 +2413,1021 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E23" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H23" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="I23" t="s">
+        <v>114</v>
+      </c>
+      <c r="J23" t="s">
+        <v>115</v>
+      </c>
+      <c r="K23" t="s">
         <v>110</v>
-      </c>
-      <c r="J23" t="s">
-        <v>111</v>
-      </c>
-      <c r="K23" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E24" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F24" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G24" t="s">
+        <v>119</v>
+      </c>
+      <c r="H24" t="s">
+        <v>120</v>
+      </c>
+      <c r="I24" t="s">
+        <v>121</v>
+      </c>
+      <c r="J24" t="s">
         <v>115</v>
       </c>
-      <c r="H24" t="s">
-        <v>116</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="K24" t="s">
         <v>117</v>
-      </c>
-      <c r="J24" t="s">
-        <v>111</v>
-      </c>
-      <c r="K24" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="D25" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E25" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F25" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H25" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I25" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J25" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K25" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="D26" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E26" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H26" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I26" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="J26" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>131</v>
       </c>
       <c r="D27" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E27" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H27" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I27" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="J27" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>135</v>
       </c>
       <c r="D28" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E28" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H28" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="I28" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="J28" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K28" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>139</v>
       </c>
       <c r="D29" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E29" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H29" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I29" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="J29" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B30" t="s">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>143</v>
       </c>
       <c r="D30" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E30" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H30" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I30" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="J30" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K30" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>147</v>
       </c>
       <c r="D31" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E31" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G31" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H31" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I31" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="J31" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K31" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>152</v>
       </c>
       <c r="D32" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F32" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G32" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H32" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="I32" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="J32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K32" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>157</v>
       </c>
       <c r="D33" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F33" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H33" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="I33" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="J33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="D34" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G34" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H34" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="I34" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="J34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K34" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="C35" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="D35" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E35" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H35" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="I35" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="J35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K35" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="C36" t="s">
-        <v>12</v>
+        <v>169</v>
       </c>
       <c r="D36" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E36" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G36" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H36" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I36" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="J36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K36" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="C37" t="s">
-        <v>12</v>
+        <v>173</v>
       </c>
       <c r="D37" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F37" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G37" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H37" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="I37" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="J37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K37" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>177</v>
       </c>
       <c r="D38" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G38" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H38" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="I38" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J38" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K38" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="C39" t="s">
-        <v>12</v>
+        <v>181</v>
       </c>
       <c r="D39" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E39" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F39" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H39" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="I39" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="J39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K39" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="C40" t="s">
-        <v>12</v>
+        <v>185</v>
       </c>
       <c r="D40" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E40" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H40" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I40" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="J40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K40" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="C41" t="s">
-        <v>12</v>
+        <v>189</v>
       </c>
       <c r="D41" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E41" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F41" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G41" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H41" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="I41" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="J41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K41" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B42" t="s">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="C42" t="s">
-        <v>12</v>
+        <v>193</v>
       </c>
       <c r="D42" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E42" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F42" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G42" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H42" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="I42" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="J42" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K42" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B43" t="s">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="C43" t="s">
-        <v>12</v>
+        <v>197</v>
       </c>
       <c r="D43" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F43" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H43" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="I43" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="J43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K43" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="C44" t="s">
-        <v>12</v>
+        <v>202</v>
       </c>
       <c r="D44" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E44" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F44" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G44" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H44" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="I44" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="J44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K44" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>206</v>
+      </c>
+      <c r="B45" t="s">
         <v>201</v>
       </c>
-      <c r="B45" t="s">
-        <v>12</v>
-      </c>
       <c r="C45" t="s">
-        <v>12</v>
+        <v>207</v>
       </c>
       <c r="D45" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E45" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F45" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H45" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="I45" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="J45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K45" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B46" t="s">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="C46" t="s">
-        <v>12</v>
+        <v>211</v>
       </c>
       <c r="D46" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H46" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="I46" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="J46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K46" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B47" t="s">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="C47" t="s">
-        <v>12</v>
+        <v>215</v>
       </c>
       <c r="D47" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E47" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F47" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G47" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H47" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="I47" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="J47" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K47" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B48" t="s">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="C48" t="s">
-        <v>12</v>
+        <v>219</v>
       </c>
       <c r="D48" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E48" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F48" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G48" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H48" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="I48" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="J48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K48" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B49" t="s">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="C49" t="s">
-        <v>12</v>
+        <v>223</v>
       </c>
       <c r="D49" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E49" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F49" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H49" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I49" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="J49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K49" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B50" t="s">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="C50" t="s">
-        <v>12</v>
+        <v>227</v>
       </c>
       <c r="D50" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E50" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F50" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G50" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H50" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="I50" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="J50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K50" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="C51" t="s">
-        <v>12</v>
+        <v>231</v>
       </c>
       <c r="D51" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E51" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F51" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G51" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H51" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="I51" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="J51" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K51" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>